--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector Returns" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top Performers" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Most Volatile" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Max Drawdown" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector Turnover" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sector Returns" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Top Performers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Most Volatile" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Max Drawdown" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sector Turnover" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Companies" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,16 +22,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -51,7 +48,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -59,19 +56,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -474,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>94.14</v>
+        <v>89.95</v>
       </c>
     </row>
     <row r="3">
@@ -487,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>59.51</v>
+        <v>56.79</v>
       </c>
     </row>
     <row r="4">
@@ -500,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>35.17</v>
+        <v>33.49</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>16.98</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="6">
@@ -526,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>4.93</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="7">
@@ -539,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>4.3</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="8">
@@ -552,7 +543,7 @@
         <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.79</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="9">
@@ -565,7 +556,7 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>-3.46</v>
+        <v>-2.72</v>
       </c>
     </row>
     <row r="10">
@@ -578,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-5.27</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="11">
@@ -591,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-10.02</v>
+        <v>-9.050000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -604,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.34</v>
+        <v>-24.98</v>
       </c>
     </row>
   </sheetData>
@@ -678,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1812</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>340.5</v>
+        <v>332.1</v>
       </c>
     </row>
     <row r="4">
@@ -718,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>301.2</v>
+        <v>267.8</v>
       </c>
     </row>
     <row r="5">
@@ -738,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>206.9</v>
+        <v>217.8</v>
       </c>
     </row>
     <row r="6">
@@ -758,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>175.4</v>
+        <v>158.8</v>
       </c>
     </row>
     <row r="7">
@@ -778,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>152.3</v>
+        <v>157.6</v>
       </c>
     </row>
     <row r="8">
@@ -798,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>120.4</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9">
@@ -818,18 +809,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>119.2</v>
+        <v>107.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>LYC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Lynas Rare Earths</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -838,27 +829,27 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>118.4</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LYC</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lynas Rare Earths</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>110.7</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="12">
@@ -878,38 +869,38 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>102</v>
+        <v>98.59999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>101.3</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -918,7 +909,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>96.3</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15">
@@ -938,38 +929,38 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>86.90000000000001</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AAI</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alcoa</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>82.09999999999999</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>AAI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Alcoa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -978,38 +969,38 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>79.40000000000001</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>78</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1018,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1038,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>75.5</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1058,7 +1049,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>72.8</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="22">
@@ -1078,47 +1069,47 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>71</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>69.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>67.90000000000001</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="25">
@@ -1138,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>67.7</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1158,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>66.09999999999999</v>
+        <v>60.2</v>
       </c>
     </row>
   </sheetData>
@@ -1219,33 +1210,33 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>141.3</v>
+        <v>141.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DRO</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>109.8</v>
+        <v>108.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>DRO</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>108.6</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="5">
@@ -1271,7 +1262,7 @@
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>81</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1297,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>76.2</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="9">
@@ -1310,7 +1301,7 @@
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>70.8</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1323,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>69</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="11">
@@ -1342,14 +1333,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>65.7</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1362,46 +1353,46 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>65.5</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>65.3</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1414,7 +1405,7 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>62.6</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="18">
@@ -1427,7 +1418,7 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>61.7</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="19">
@@ -1453,7 +1444,7 @@
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>60.7</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="21">
@@ -1463,7 +1454,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C21" t="n">
         <v>60.4</v>
@@ -1479,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>60.2</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="23">
@@ -1492,7 +1483,7 @@
         <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>59.6</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="24">
@@ -1505,7 +1496,7 @@
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>59</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1509,7 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>58.8</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="26">
@@ -2006,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.46</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="3">
@@ -2016,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.41</v>
+        <v>45.49</v>
       </c>
     </row>
     <row r="4">
@@ -2026,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.15</v>
+        <v>44.17</v>
       </c>
     </row>
     <row r="5">
@@ -2036,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.46</v>
+        <v>39.47</v>
       </c>
     </row>
     <row r="6">
@@ -2046,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.78</v>
+        <v>36.89</v>
       </c>
     </row>
     <row r="7">
@@ -2056,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.18</v>
+        <v>33.17</v>
       </c>
     </row>
     <row r="8">
@@ -2066,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.25</v>
+        <v>27.31</v>
       </c>
     </row>
     <row r="9">
@@ -2076,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.18</v>
+        <v>26.23</v>
       </c>
     </row>
     <row r="10">
@@ -2086,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21.77</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="11">
@@ -2096,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.15</v>
+        <v>21.17</v>
       </c>
     </row>
     <row r="12">
@@ -2106,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.72</v>
+        <v>13.73</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>89.95</v>
+        <v>78.52</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>56.79</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>33.49</v>
+        <v>32.34</v>
       </c>
     </row>
     <row r="5">
@@ -504,33 +504,33 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>14.76</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>4.23</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>4.06</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="8">
@@ -543,33 +543,33 @@
         <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.52</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-2.72</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-3.21</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-9.050000000000001</v>
+        <v>-9.789999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-24.98</v>
+        <v>-25.25</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1728</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>332.1</v>
+        <v>283.3</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>267.8</v>
+        <v>256.2</v>
       </c>
     </row>
     <row r="5">
@@ -729,47 +729,47 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>217.8</v>
+        <v>202.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>158.8</v>
+        <v>155.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>157.6</v>
+        <v>137.1</v>
       </c>
     </row>
     <row r="8">
@@ -789,18 +789,18 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>124</v>
+        <v>120.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>LYC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Iluka Resources</t>
+          <t>Lynas Rare Earths</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -809,18 +809,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>107.4</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LYC</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lynas Rare Earths</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>106.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>101.3</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,18 +869,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>98.59999999999999</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>93.90000000000001</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Iluka Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,18 +909,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>92</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>87.3</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="16">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>78.2</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="17">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>76.09999999999999</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>74.90000000000001</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>72.59999999999999</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>69.90000000000001</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
@@ -1049,58 +1049,58 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>68.8</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>66.59999999999999</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>66.59999999999999</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,47 +1109,47 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>65.8</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>61.8</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>60.2</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>141.5</v>
+        <v>141.8</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>108.3</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="5">
@@ -1262,7 +1262,7 @@
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>81.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>69.3</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1346,40 +1346,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>65.90000000000001</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>65.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>65.40000000000001</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>65.09999999999999</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="17">
@@ -1405,7 +1405,7 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>62.8</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="18">
@@ -1418,7 +1418,7 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>61.9</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C21" t="n">
-        <v>60.4</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="22">
@@ -1681,46 +1681,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XRO</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Xero</t>
+          <t>Telix Pharmaceuticals</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-66.5</v>
+        <v>-66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Telix Pharmaceuticals</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-66</v>
+        <v>-65.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>XRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>Xero</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-65.3</v>
+        <v>-64.7</v>
       </c>
     </row>
     <row r="12">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-54</v>
+        <v>-55.6</v>
       </c>
     </row>
     <row r="20">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.53</v>
+        <v>48.57</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.49</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.17</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.47</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.89</v>
+        <v>36.96</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.17</v>
+        <v>33.13</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.31</v>
+        <v>27.38</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.23</v>
+        <v>26.27</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21.8</v>
+        <v>21.81</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.17</v>
+        <v>21.18</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.73</v>
+        <v>13.75</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>78.52</v>
+        <v>94.70999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>55.41</v>
+        <v>54.68</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>32.34</v>
+        <v>31.79</v>
       </c>
     </row>
     <row r="5">
@@ -504,33 +504,33 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>13.43</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>3.73</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="8">
@@ -556,7 +556,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-2.83</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-3.41</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-9.789999999999999</v>
+        <v>-8.51</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.25</v>
+        <v>-25</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1564</v>
+        <v>1812.5</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>283.3</v>
+        <v>280.5</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>256.2</v>
+        <v>238.9</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>202.1</v>
+        <v>188.3</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>155.8</v>
+        <v>150.5</v>
       </c>
     </row>
     <row r="7">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>120.7</v>
+        <v>118.5</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>101.5</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="10">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>100</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="11">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>97.09999999999999</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Iluka Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>89.5</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="13">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>86.59999999999999</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Iluka Resources</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,58 +909,58 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>86.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>82.3</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>AAI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Alcoa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>81.2</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AAI</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alcoa</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>80.09999999999999</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>75.2</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>73.8</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>72</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>70.09999999999999</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>69.5</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,67 +1089,67 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>66.7</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>66.40000000000001</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>65.90000000000001</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>63</v>
+        <v>63.2</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C2" t="n">
-        <v>141.8</v>
+        <v>142.3</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C3" t="n">
-        <v>108.5</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C4" t="n">
-        <v>107.8</v>
+        <v>107.9</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C5" t="n">
-        <v>81.59999999999999</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C7" t="n">
-        <v>78.90000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C8" t="n">
-        <v>76.3</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C9" t="n">
-        <v>71.09999999999999</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C10" t="n">
-        <v>69.40000000000001</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C11" t="n">
-        <v>67.2</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C12" t="n">
-        <v>66.59999999999999</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C13" t="n">
-        <v>66.09999999999999</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C14" t="n">
-        <v>65.90000000000001</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C15" t="n">
-        <v>65.7</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C16" t="n">
-        <v>65.3</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="17">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C17" t="n">
-        <v>62.6</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="18">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C18" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="19">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C19" t="n">
         <v>61.7</v>
@@ -1441,36 +1441,36 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C20" t="n">
-        <v>60.8</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>183</v>
+        <v>253</v>
       </c>
       <c r="C21" t="n">
-        <v>60.3</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>254</v>
+        <v>184</v>
       </c>
       <c r="C22" t="n">
-        <v>60.3</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="23">
@@ -1480,36 +1480,36 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C23" t="n">
-        <v>59.7</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C24" t="n">
-        <v>59.1</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C25" t="n">
-        <v>58.9</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="26">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C26" t="n">
-        <v>58.3</v>
+        <v>58.7</v>
       </c>
     </row>
   </sheetData>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-64.7</v>
+        <v>-64.3</v>
       </c>
     </row>
     <row r="12">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.57</v>
+        <v>48.58</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.62</v>
+        <v>45.49</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.2</v>
+        <v>44.18</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.51</v>
+        <v>39.53</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.96</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.13</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.38</v>
+        <v>27.44</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.27</v>
+        <v>26.31</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21.81</v>
+        <v>21.84</v>
       </c>
     </row>
     <row r="11">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.75</v>
+        <v>13.77</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>94.70999999999999</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>54.68</v>
+        <v>51.45</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>31.79</v>
+        <v>32.76</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>13.06</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>3.46</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="7">
@@ -530,33 +530,33 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>2.67</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.66</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.49</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-3.07</v>
+        <v>-3.57</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-8.51</v>
+        <v>-7.48</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-25</v>
+        <v>-25.02</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1812.5</v>
+        <v>1787.5</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>280.5</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>238.9</v>
+        <v>261.4</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>188.3</v>
+        <v>187.9</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>150.5</v>
+        <v>158.1</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>137.1</v>
+        <v>140.7</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>118.5</v>
+        <v>121.9</v>
       </c>
     </row>
     <row r="9">
@@ -809,47 +809,47 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>115.1</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>96.5</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>95.7</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -869,38 +869,38 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>85.7</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>85.5</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,38 +909,38 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>84.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>80.3</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AAI</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alcoa</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,18 +949,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>75.59999999999999</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>AAI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Alcoa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>75.5</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,38 +989,38 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>70.7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>69.59999999999999</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>69.5</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,38 +1049,38 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>69.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>69.09999999999999</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,38 +1089,38 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>68.90000000000001</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>67.2</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>66.8</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>63.2</v>
+        <v>54.9</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>142.3</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C3" t="n">
         <v>108.6</v>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>107.9</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>81.8</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>81.7</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>76.90000000000001</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>70.90000000000001</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>69.5</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="12">
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C12" t="n">
         <v>66.8</v>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>66.2</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>65.8</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>65.2</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>62.7</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="18">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>61.9</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="19">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.7</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="20">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C20" t="n">
         <v>61</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>60.4</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C22" t="n">
-        <v>60.1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23">
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C23" t="n">
         <v>59.6</v>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>59.5</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="25">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" t="n">
         <v>59.1</v>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>58.7</v>
+        <v>58.6</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.58</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.49</v>
+        <v>45.52</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.18</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.53</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.98</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="7">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.44</v>
+        <v>27.46</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.31</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21.84</v>
+        <v>21.87</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.18</v>
+        <v>21.23</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.77</v>
+        <v>13.78</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>93.09999999999999</v>
+        <v>77.91</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>51.45</v>
+        <v>50.62</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>32.76</v>
+        <v>30.55</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>12.58</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>4.42</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>3.72</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.15</v>
+        <v>-3.68</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-2.23</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-3.57</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-7.48</v>
+        <v>-7.37</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.02</v>
+        <v>-25.46</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1787.5</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>276</v>
+        <v>277.1</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>261.4</v>
+        <v>238.1</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>187.9</v>
+        <v>190.7</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>158.1</v>
+        <v>159.2</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>140.7</v>
+        <v>148.2</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>121.9</v>
+        <v>124.6</v>
       </c>
     </row>
     <row r="9">
@@ -809,58 +809,58 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>109.8</v>
+        <v>115.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Iluka Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>92.3</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>91.59999999999999</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Iluka Resources</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,47 +869,47 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>87.5</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>82.59999999999999</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>82.59999999999999</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="15">
@@ -929,18 +929,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>76.7</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,18 +949,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>76.59999999999999</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AAI</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alcoa</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,67 +969,67 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>73</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>71</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>70.5</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>68.40000000000001</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="21">
@@ -1049,38 +1049,38 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>67.90000000000001</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>65.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>AAI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Alcoa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>65.09999999999999</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="24">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>IMD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>IMDEX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>55.2</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>54.9</v>
+        <v>52.6</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>142</v>
+        <v>142.6</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>108.6</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>107.8</v>
+        <v>107.1</v>
       </c>
     </row>
     <row r="5">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>76.8</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="9">
@@ -1301,7 +1301,7 @@
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>70.8</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="10">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>69.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1327,7 +1327,7 @@
         <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>68.2</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1340,46 +1340,46 @@
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>66.8</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>66.09999999999999</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>66.09999999999999</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>65.7</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="16">
@@ -1405,7 +1405,7 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>62.6</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="18">
@@ -1418,7 +1418,7 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.4</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="19">
@@ -1431,7 +1431,7 @@
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.6</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="20">
@@ -1444,7 +1444,7 @@
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="21">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C22" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="23">
@@ -1483,7 +1483,7 @@
         <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="24">
@@ -1509,7 +1509,7 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>59.1</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26">
@@ -1522,7 +1522,7 @@
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>58.6</v>
+        <v>58.7</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.6</v>
+        <v>48.51</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.52</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.22</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.51</v>
+        <v>39.48</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.99</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.07</v>
+        <v>33.12</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.46</v>
+        <v>27.48</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.32</v>
+        <v>26.31</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21.87</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.23</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="12">

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>77.91</v>
+        <v>78.61</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>50.62</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>30.55</v>
+        <v>29.95</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>12.4</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>5.13</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>2.97</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.68</v>
+        <v>-4.46</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-3.78</v>
+        <v>-5.29</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-5.2</v>
+        <v>-7.28</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-7.37</v>
+        <v>-7.73</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.46</v>
+        <v>-26.24</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1549</v>
+        <v>1557.1</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>277.1</v>
+        <v>274.5</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>238.1</v>
+        <v>257.5</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>190.7</v>
+        <v>181.1</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>159.2</v>
+        <v>152.3</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>148.2</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>124.6</v>
+        <v>123.4</v>
       </c>
     </row>
     <row r="9">
@@ -809,18 +809,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>115.6</v>
+        <v>113.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Iluka Resources</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,38 +829,38 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>91.8</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>87.7</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Iluka Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,127 +869,127 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>84.59999999999999</v>
+        <v>87.59999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>81.8</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>80.3</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>78.7</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>74.5</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>72.2</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>71.5</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1009,38 +1009,38 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>70.7</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>69.5</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>67.8</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>63.6</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AAI</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Alcoa</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>60.4</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>55.9</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IMD</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IMDEX</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>55.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>52.6</v>
+        <v>54.6</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>142.6</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>107.1</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5">
@@ -1262,7 +1262,7 @@
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>76.7</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="9">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>69.59999999999999</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="11">
@@ -1340,7 +1340,7 @@
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>66.90000000000001</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>66.2</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="14">
@@ -1372,27 +1372,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>65.3</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>65.09999999999999</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="17">
@@ -1418,7 +1418,7 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.2</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="19">
@@ -1431,7 +1431,7 @@
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.8</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="20">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>60.5</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C22" t="n">
-        <v>59.9</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="23">
@@ -1509,7 +1509,7 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>59</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="26">
@@ -1522,7 +1522,7 @@
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>58.7</v>
+        <v>58.6</v>
       </c>
     </row>
   </sheetData>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-64.3</v>
+        <v>-64.09999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.2</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="5">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.12</v>
+        <v>33.18</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.48</v>
+        <v>27.52</v>
       </c>
     </row>
     <row r="9">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21.9</v>
+        <v>21.94</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.2</v>
+        <v>21.18</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.78</v>
+        <v>13.79</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>78.61</v>
+        <v>87.02</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>50.3</v>
+        <v>52.43</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>29.95</v>
+        <v>30.76</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>11.91</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>4.8</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.46</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="9">
@@ -556,33 +556,33 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.29</v>
+        <v>-5.46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-7.28</v>
+        <v>-6.51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-7.73</v>
+        <v>-6.79</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-26.24</v>
+        <v>-25.16</v>
       </c>
     </row>
   </sheetData>
@@ -669,47 +669,47 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1557.1</v>
+        <v>1670.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>274.5</v>
+        <v>271.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>257.5</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>181.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>152.3</v>
+        <v>144.3</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>138.6</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>123.4</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>113.8</v>
+        <v>118.5</v>
       </c>
     </row>
     <row r="10">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>91.5</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="11">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>89.59999999999999</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="12">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>87.59999999999999</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="13">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>85.09999999999999</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,118 +909,118 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>79.2</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>73.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>72.40000000000001</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>70.7</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>67.40000000000001</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>66.8</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>64.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>64.8</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>61</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>60.9</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>56.7</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>55.2</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>54.6</v>
+        <v>59.3</v>
       </c>
     </row>
   </sheetData>
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>108.7</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>107</v>
+        <v>107.1</v>
       </c>
     </row>
     <row r="5">
@@ -1262,7 +1262,7 @@
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79.40000000000001</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="8">
@@ -1288,33 +1288,33 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>76.5</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>70.7</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>69.8</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="11">
@@ -1340,7 +1340,7 @@
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>67</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>66.3</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1372,92 +1372,92 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>65.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>64.7</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>62.5</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.4</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.9</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.1</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>60.6</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C22" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="23">
@@ -1509,7 +1509,7 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>59.2</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="26">
@@ -1522,7 +1522,7 @@
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>58.6</v>
+        <v>58.5</v>
       </c>
     </row>
   </sheetData>
@@ -1921,31 +1921,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>REA</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>REA Group</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-49.4</v>
+        <v>-49.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PMV</t>
+          <t>REA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Premier Investments</t>
+          <t>REA Group</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-49.1</v>
+        <v>-49.4</v>
       </c>
     </row>
   </sheetData>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.33</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.19</v>
+        <v>44.08</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.48</v>
+        <v>39.47</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.98</v>
+        <v>36.95</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.18</v>
+        <v>33.11</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.52</v>
+        <v>27.54</v>
       </c>
     </row>
     <row r="9">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21.94</v>
+        <v>21.96</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.18</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.79</v>
+        <v>13.81</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>87.02</v>
+        <v>90.55</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>52.43</v>
+        <v>55.18</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>30.76</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>11.22</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>6.25</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>0.82</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.19</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.46</v>
+        <v>-5.57</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-6.51</v>
+        <v>-6.29</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-6.79</v>
+        <v>-8.02</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.16</v>
+        <v>-25.07</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1670.8</v>
+        <v>1716.7</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>271.8</v>
+        <v>279.7</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>243</v>
+        <v>254.5</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>166.2</v>
+        <v>163.9</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>144.3</v>
+        <v>141.9</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>132</v>
+        <v>131.5</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>125.5</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>118.5</v>
+        <v>121.9</v>
       </c>
     </row>
     <row r="10">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>107.2</v>
+        <v>116.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>93.7</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Iluka Resources</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,27 +869,27 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>85.7</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Iluka Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>81.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -909,58 +909,58 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>80.3</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>75.59999999999999</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>75.40000000000001</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,58 +969,58 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>73.8</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>69.7</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>68.90000000000001</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,47 +1049,47 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>67.7</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>66.90000000000001</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>63</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="24">
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61.9</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="25">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>60.5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C2" t="n">
-        <v>142.5</v>
+        <v>142.8</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C3" t="n">
-        <v>108.6</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="4">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C4" t="n">
         <v>107.1</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C5" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="6">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
         <v>81.5</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C7" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C8" t="n">
-        <v>76.7</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="9">
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C9" t="n">
         <v>72.40000000000001</v>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C10" t="n">
-        <v>70.7</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C11" t="n">
-        <v>68.09999999999999</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="12">
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C12" t="n">
         <v>67.09999999999999</v>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C13" t="n">
-        <v>66.40000000000001</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C15" t="n">
-        <v>64.59999999999999</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C16" t="n">
-        <v>64.3</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="17">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C17" t="n">
-        <v>62.8</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C18" t="n">
-        <v>62.5</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="19">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C19" t="n">
         <v>62.3</v>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C20" t="n">
-        <v>61.9</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="21">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C21" t="n">
         <v>61.4</v>
@@ -1463,14 +1463,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>188</v>
+        <v>253</v>
       </c>
       <c r="C22" t="n">
-        <v>59.6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23">
@@ -1480,36 +1480,36 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C23" t="n">
-        <v>59.5</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C24" t="n">
-        <v>59.4</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>254</v>
+        <v>189</v>
       </c>
       <c r="C25" t="n">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="26">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C26" t="n">
-        <v>58.5</v>
+        <v>58.7</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.51</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.11</v>
+        <v>45.16</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.08</v>
+        <v>44.05</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.47</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.95</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.11</v>
+        <v>33.13</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.54</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.31</v>
+        <v>26.34</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21.96</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.15</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.81</v>
+        <v>13.83</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>90.55</v>
+        <v>91.77</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>55.18</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>29.22</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>11.17</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>5.42</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.66</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="8">
@@ -543,33 +543,33 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.25</v>
+        <v>-4.64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.57</v>
+        <v>-5.44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>-6.29</v>
+        <v>-7.04</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-8.02</v>
+        <v>-7.7</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.07</v>
+        <v>-24.63</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1716.7</v>
+        <v>1741.7</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>279.7</v>
+        <v>267.4</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>254.5</v>
+        <v>235.2</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>163.9</v>
+        <v>149.2</v>
       </c>
     </row>
     <row r="6">
@@ -749,47 +749,47 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>141.9</v>
+        <v>144.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>131.5</v>
+        <v>128.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>127.2</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>121.9</v>
+        <v>107.7</v>
       </c>
     </row>
     <row r="10">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>116.4</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="11">
@@ -849,38 +849,38 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>106.2</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>85.2</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Iluka Resources</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>83.90000000000001</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Iluka Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,27 +909,27 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>81.40000000000001</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>80.5</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>75.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>75.40000000000001</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>73.40000000000001</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,38 +1009,38 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>71.8</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>70.3</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,58 +1049,58 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>69.3</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>68.8</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>68.5</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>64.3</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="25">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>62</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>59.2</v>
+        <v>55.9</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>142.8</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>108.8</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="4">
@@ -1233,20 +1233,20 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>107.1</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TUA</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C5" t="n">
         <v>81.7</v>
@@ -1255,14 +1255,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>TUA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
         <v>79.59999999999999</v>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>76.8</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72.40000000000001</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>70.8</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C11" t="n">
         <v>68.2</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>67.09999999999999</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C13" t="n">
         <v>66.5</v>
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" t="n">
         <v>66.09999999999999</v>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>64.7</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>64.2</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C17" t="n">
         <v>63</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C18" t="n">
         <v>62.7</v>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>62.3</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>62.1</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>61.4</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>60</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="23">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>59.6</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="24">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C24" t="n">
         <v>59.6</v>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C25" t="n">
-        <v>59.5</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="26">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" t="n">
         <v>58.7</v>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-53.3</v>
+        <v>-53.4</v>
       </c>
     </row>
     <row r="21">
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-49.5</v>
+        <v>-50.1</v>
       </c>
     </row>
     <row r="26">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.53</v>
+        <v>48.49</v>
       </c>
     </row>
     <row r="3">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.05</v>
+        <v>44.02</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.5</v>
+        <v>39.46</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.98</v>
+        <v>36.97</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.13</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.6</v>
+        <v>27.57</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.34</v>
+        <v>26.33</v>
       </c>
     </row>
     <row r="10">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.16</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="12">

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>91.77</v>
+        <v>78.45</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>49.51</v>
+        <v>44.32</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>29.22</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>8.42</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>5.85</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.22</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="8">
@@ -543,33 +543,33 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.64</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.44</v>
+        <v>-4.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-7.04</v>
+        <v>-6.68</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-7.7</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-24.63</v>
+        <v>-25.02</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1741.7</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>267.4</v>
+        <v>227.7</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>235.2</v>
+        <v>217.6</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>149.2</v>
+        <v>143.2</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>144.4</v>
+        <v>140.4</v>
       </c>
     </row>
     <row r="7">
@@ -769,18 +769,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>128.4</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>LYC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>Lynas Rare Earths</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,18 +789,18 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LYC</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lynas Rare Earths</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>107.7</v>
+        <v>106.3</v>
       </c>
     </row>
     <row r="10">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>107.5</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>101.8</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="12">
@@ -869,27 +869,27 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>80.5</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>77.3</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -909,78 +909,78 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>76.2</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>70.90000000000001</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>70.40000000000001</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>67.59999999999999</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,58 +989,58 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>66.5</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>66.2</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>64.90000000000001</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>63.8</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>63</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>61.4</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>60.3</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>AAI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Alcoa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>58.9</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>55.9</v>
+        <v>49.7</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>142.5</v>
+        <v>142.7</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>108.6</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="4">
@@ -1249,7 +1249,7 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="6">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79.59999999999999</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="8">
@@ -1301,7 +1301,7 @@
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72.5</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>66.5</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
         <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>64.40000000000001</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="17">
@@ -1405,7 +1405,7 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="18">
@@ -1418,33 +1418,33 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.7</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>62.5</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>62</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>61.5</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="22">
@@ -1470,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>60.2</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="23">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C25" t="n">
-        <v>59.4</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="26">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-53.4</v>
+        <v>-54</v>
       </c>
     </row>
     <row r="21">
@@ -1891,46 +1891,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Catalyst Metals</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-51</v>
+        <v>-51.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TNE</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TechnologyOne</t>
+          <t>Catalyst Metals</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-50.6</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>TNE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>TechnologyOne</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-50.1</v>
+        <v>-50.6</v>
       </c>
     </row>
     <row r="26">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.49</v>
+        <v>48.59</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.16</v>
+        <v>45.25</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.02</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.46</v>
+        <v>39.55</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.97</v>
+        <v>37.02</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.1</v>
+        <v>33.15</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.57</v>
+        <v>27.64</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.33</v>
+        <v>26.41</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21.99</v>
+        <v>22.12</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.15</v>
+        <v>21.19</v>
       </c>
     </row>
     <row r="12">

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>78.45</v>
+        <v>86.72</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>44.32</v>
+        <v>44.78</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>26.8</v>
+        <v>26.51</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>9.74</v>
+        <v>12.97</v>
       </c>
     </row>
     <row r="6">
@@ -517,59 +517,59 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>5.62</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.26</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.83</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.75</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>-6.68</v>
+        <v>-4.86</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-7.59</v>
+        <v>-8.01</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.02</v>
+        <v>-24.61</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1540</v>
+        <v>1665.2</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.7</v>
+        <v>214.7</v>
       </c>
     </row>
     <row r="4">
@@ -709,67 +709,67 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>217.6</v>
+        <v>206.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>143.2</v>
+        <v>141.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>140.4</v>
+        <v>139.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>128.5</v>
+        <v>137.7</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>107</v>
+        <v>103.6</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>106.3</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="10">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>96.40000000000001</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>81.2</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="12">
@@ -869,38 +869,38 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>79</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>73.90000000000001</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Iluka Resources</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,18 +909,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>70</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Iluka Resources</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,98 +929,98 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>66.7</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>63.6</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>63.1</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>62.1</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>61.3</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>57.9</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>57.9</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="23">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>57.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>56.7</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AAI</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Alcoa</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>55.7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>49.7</v>
+        <v>53.6</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>142.7</v>
+        <v>142.4</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>108.9</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="4">
@@ -1242,27 +1242,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>TUA</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TUA</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79.3</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>71</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1340,7 +1340,7 @@
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>68.09999999999999</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>66.59999999999999</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="14">
@@ -1366,7 +1366,7 @@
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>66.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>64.59999999999999</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="16">
@@ -1405,7 +1405,7 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>63.1</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="18">
@@ -1418,7 +1418,7 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.6</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="19">
@@ -1444,7 +1444,7 @@
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.8</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="21">
@@ -1496,7 +1496,7 @@
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>59.6</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="25">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C25" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="26">
@@ -1522,7 +1522,7 @@
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>58.7</v>
+        <v>58.5</v>
       </c>
     </row>
   </sheetData>
@@ -1876,31 +1876,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LOV</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lovisa</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-51.5</v>
+        <v>-52</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>LOV</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>Lovisa</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-51.2</v>
+        <v>-51.5</v>
       </c>
     </row>
     <row r="24">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.25</v>
+        <v>45.23</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.1</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.55</v>
+        <v>39.61</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37.02</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.15</v>
+        <v>33.11</v>
       </c>
     </row>
     <row r="8">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.41</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.12</v>
+        <v>22.13</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.19</v>
+        <v>21.17</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.83</v>
+        <v>13.82</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>86.72</v>
+        <v>81.41</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>44.78</v>
+        <v>45.76</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>26.51</v>
+        <v>24.96</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>12.97</v>
+        <v>15.58</v>
       </c>
     </row>
     <row r="6">
@@ -517,59 +517,59 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>5.77</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>0.09</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.21</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.19</v>
+        <v>-5.21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-4.86</v>
+        <v>-5.23</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-8.01</v>
+        <v>-9.51</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-24.61</v>
+        <v>-24.56</v>
       </c>
     </row>
   </sheetData>
@@ -669,47 +669,47 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1665.2</v>
+        <v>1585.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>214.7</v>
+        <v>203.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>206.3</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5">
@@ -729,58 +729,58 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>141.5</v>
+        <v>143.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>139.9</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>137.7</v>
+        <v>133.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LYC</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lynas Rare Earths</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,18 +789,18 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>103.6</v>
+        <v>111.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>LYC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>Lynas Rare Earths</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -809,18 +809,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>96.7</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>95</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>88.8</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="12">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>74</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,58 +909,58 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>69.09999999999999</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Iluka Resources</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>66.90000000000001</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>66.7</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Iluka Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,58 +969,58 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>66.09999999999999</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>65.59999999999999</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>65.40000000000001</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>62.3</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>58.3</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>56.5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>55.2</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>54.4</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>54</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>AAI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Alcoa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>53.6</v>
+        <v>52.6</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>142.4</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>108.8</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4">
@@ -1262,7 +1262,7 @@
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>81.7</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>76.7</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1301,7 +1301,7 @@
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="10">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>70.59999999999999</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
@@ -1340,7 +1340,7 @@
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="13">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>64.7</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1405,7 +1405,7 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>62.9</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
@@ -1431,7 +1431,7 @@
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>62.3</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="20">
@@ -1444,7 +1444,7 @@
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.5</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>61.4</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="22">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C25" t="n">
-        <v>59.1</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="26">
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-66</v>
+        <v>-65.8</v>
       </c>
     </row>
     <row r="10">
@@ -1756,12 +1756,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Austal</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1771,31 +1771,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ARB Corporation</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-57.3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Austal</t>
+          <t>ARB Corporation</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-57</v>
+        <v>-57.3</v>
       </c>
     </row>
     <row r="17">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-52</v>
+        <v>-52.1</v>
       </c>
     </row>
     <row r="23">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.23</v>
+        <v>45.22</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.07</v>
+        <v>44.05</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.61</v>
+        <v>39.59</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.11</v>
+        <v>33.08</v>
       </c>
     </row>
     <row r="8">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.4</v>
+        <v>26.42</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.13</v>
+        <v>22.14</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.17</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.82</v>
+        <v>13.79</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>81.41</v>
+        <v>80.08</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>45.76</v>
+        <v>40.42</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>24.96</v>
+        <v>22.15</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>15.58</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>5.65</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>0.44</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.93</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.21</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-5.23</v>
+        <v>-6.29</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-9.51</v>
+        <v>-8.449999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-24.56</v>
+        <v>-23.89</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1585.1</v>
+        <v>1554.2</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>203.6</v>
+        <v>171.5</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>190</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5">
@@ -729,47 +729,47 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>143.8</v>
+        <v>133.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>133.3</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8">
@@ -789,18 +789,18 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>111.2</v>
+        <v>103.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LYC</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lynas Rare Earths</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -809,78 +809,78 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>100.6</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>92.3</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>86.3</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>79.8</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>73.2</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,58 +909,58 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>72.3</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>LYC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Lynas Rare Earths</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>70.59999999999999</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>69.59999999999999</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Iluka Resources</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,78 +969,78 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>69.40000000000001</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>66.3</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>65.7</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>58.5</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>57.9</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>56.2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>AAI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Alcoa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>54.5</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AAI</t>
+          <t>CSC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alcoa</t>
+          <t>Capstone Copper</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>52.6</v>
+        <v>47.4</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C2" t="n">
-        <v>142.5</v>
+        <v>142.8</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C3" t="n">
-        <v>109</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C4" t="n">
-        <v>107</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C5" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
-        <v>81.40000000000001</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C7" t="n">
-        <v>79.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C8" t="n">
-        <v>76.59999999999999</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C9" t="n">
-        <v>72.2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C10" t="n">
-        <v>71</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C11" t="n">
-        <v>68.2</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C12" t="n">
-        <v>67.8</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C13" t="n">
-        <v>66.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C14" t="n">
-        <v>65.59999999999999</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C15" t="n">
-        <v>64.90000000000001</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="16">
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C16" t="n">
         <v>64.5</v>
@@ -1402,127 +1402,127 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C18" t="n">
-        <v>62.7</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C19" t="n">
-        <v>62.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C20" t="n">
-        <v>61.7</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C21" t="n">
-        <v>61.3</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C22" t="n">
-        <v>60.6</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LYC</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>254</v>
+        <v>194</v>
       </c>
       <c r="C23" t="n">
-        <v>59.9</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C24" t="n">
-        <v>59.4</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c r="C25" t="n">
-        <v>58.9</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>LYC</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C26" t="n">
-        <v>58.5</v>
+        <v>57.8</v>
       </c>
     </row>
   </sheetData>
@@ -1726,46 +1726,46 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Seek</t>
+          <t>Austal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-58.7</v>
+        <v>-59.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TWE</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Treasury Wine Estates</t>
+          <t>Seek</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-57.6</v>
+        <v>-58.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>TWE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Austal</t>
+          <t>Treasury Wine Estates</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-57.5</v>
+        <v>-57.6</v>
       </c>
     </row>
     <row r="15">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-52.1</v>
+        <v>-52.8</v>
       </c>
     </row>
     <row r="23">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.59</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.22</v>
+        <v>45.26</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.05</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.59</v>
+        <v>39.71</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.99</v>
+        <v>37.04</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.08</v>
+        <v>33.14</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.64</v>
+        <v>27.68</v>
       </c>
     </row>
     <row r="9">
@@ -2067,27 +2067,27 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.42</v>
+        <v>26.47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.14</v>
+        <v>22.39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.15</v>
+        <v>22.18</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.79</v>
+        <v>13.83</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>80.08</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>40.42</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="4">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>13.85</v>
+        <v>14.07</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>5.69</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>1.03</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.38</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-2.96</v>
+        <v>-4.01</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-6.29</v>
+        <v>-6.68</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-8.449999999999999</v>
+        <v>-8.130000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-23.89</v>
+        <v>-23.56</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1554.2</v>
+        <v>1529.2</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>171.5</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>140</v>
+        <v>138.5</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>133.9</v>
+        <v>133.2</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>127</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>108</v>
+        <v>111.1</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>103.7</v>
+        <v>106.6</v>
       </c>
     </row>
     <row r="9">
@@ -809,58 +809,58 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>91.5</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>76.8</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>75.7</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,18 +869,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>70.7</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>68.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -909,58 +909,58 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>66.3</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LYC</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lynas Rare Earths</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>62.5</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>LYC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Lynas Rare Earths</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>60.9</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>60.1</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>58.8</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>58.2</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="20">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>54.6</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>54.6</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="22">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>54</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>AAI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Alcoa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>53.1</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="24">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>53</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AAI</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Alcoa</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>51.2</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CSC</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capstone Copper</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>47.4</v>
+        <v>49.6</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>142.8</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>108.3</v>
+        <v>108.1</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>105.8</v>
+        <v>105.6</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>81.8</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>81.7</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>78.40000000000001</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>76.8</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>71.09999999999999</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>68.40000000000001</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>68.09999999999999</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>66.7</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>65.8</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>65.2</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>64.5</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="17">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>63.1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.8</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="19">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.9</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.4</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>60.7</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>59.4</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="23">
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C23" t="n">
         <v>58.8</v>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>58.7</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="25">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>58.5</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="26">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.8</v>
+        <v>57.6</v>
       </c>
     </row>
   </sheetData>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-59.6</v>
+        <v>-59.7</v>
       </c>
     </row>
     <row r="13">
@@ -1855,33 +1855,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-54</v>
+        <v>-54.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-52.8</v>
+        <v>-53.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.65</v>
+        <v>48.59</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.26</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.07</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.71</v>
+        <v>39.73</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37.04</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.14</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.68</v>
+        <v>27.66</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.47</v>
+        <v>26.45</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.39</v>
+        <v>22.36</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.18</v>
+        <v>22.16</v>
       </c>
     </row>
     <row r="12">

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>78.5</v>
+        <v>74.52</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>41.62</v>
+        <v>41.85</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>22.15</v>
+        <v>21.22</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>14.07</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>4.96</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>0.65</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.47</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.01</v>
+        <v>-4.83</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-6.68</v>
+        <v>-7.66</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-8.130000000000001</v>
+        <v>-8.51</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-23.56</v>
+        <v>-25.04</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1529.2</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="3">
@@ -689,27 +689,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>174.5</v>
+        <v>194.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>138.5</v>
+        <v>130.9</v>
       </c>
     </row>
     <row r="5">
@@ -729,27 +729,27 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>133.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>126.7</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>111.1</v>
+        <v>118.5</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>106.6</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>94.2</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="10">
@@ -829,27 +829,27 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>79.59999999999999</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>71.7</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -869,27 +869,27 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>70.59999999999999</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>70.09999999999999</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -909,27 +909,27 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>69.2</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>63.4</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="16">
@@ -949,18 +949,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>62.4</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>59.4</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,58 +989,58 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>58.2</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>57.5</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>57.4</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>CSC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Capstone Copper</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>56.5</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>AAI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Alcoa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>55.8</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AAI</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Alcoa</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>54.7</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,38 +1109,38 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>53.9</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Mesoblast</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>52.7</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>49.6</v>
+        <v>51.1</v>
       </c>
     </row>
   </sheetData>
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>108.1</v>
+        <v>107.6</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>105.6</v>
+        <v>104.7</v>
       </c>
     </row>
     <row r="5">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>76.7</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1314,33 +1314,33 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>71.2</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>68.3</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="13">
@@ -1366,7 +1366,7 @@
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>65.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>64.3</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="17">
@@ -1418,7 +1418,7 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.6</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="19">
@@ -1431,7 +1431,7 @@
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.8</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="20">
@@ -1470,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="23">
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C23" t="n">
         <v>58.8</v>
@@ -1522,7 +1522,7 @@
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.6</v>
+        <v>57.7</v>
       </c>
     </row>
   </sheetData>
@@ -1846,31 +1846,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deep Yellow</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-54.6</v>
+        <v>-55</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>Deep Yellow</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-53.5</v>
+        <v>-54.6</v>
       </c>
     </row>
     <row r="22">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.59</v>
+        <v>48.62</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.2</v>
+        <v>45.18</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>44.04</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.73</v>
+        <v>39.81</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>37.02</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.1</v>
+        <v>33.13</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.66</v>
+        <v>27.68</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.45</v>
+        <v>26.47</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.36</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="11">

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>74.52</v>
+        <v>68.84999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>41.85</v>
+        <v>42.52</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>21.22</v>
+        <v>21.37</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>12.12</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>4.27</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>1.05</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.69</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="9">
@@ -556,33 +556,33 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.83</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-7.66</v>
+        <v>-6.74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-8.51</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.04</v>
+        <v>-24.11</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1460</v>
+        <v>1357.7</v>
       </c>
     </row>
     <row r="3">
@@ -689,87 +689,87 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>194.6</v>
+        <v>189.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>130.9</v>
+        <v>132.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>130.5</v>
+        <v>127.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>122</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>118.5</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>109</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>88.3</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="10">
@@ -829,38 +829,38 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>77.3</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>73.90000000000001</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,38 +869,38 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>72.3</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>66.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,27 +909,27 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>65.2</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>65.2</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="16">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>64.59999999999999</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="17">
@@ -969,47 +969,47 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>60.3</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Mesoblast</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60.1</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>AAI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Alcoa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>59.9</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="20">
@@ -1029,38 +1029,38 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>59.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CSC</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capstone Copper</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>56.8</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AAI</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alcoa</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>56.7</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>56.5</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,38 +1109,38 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>53.8</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mesoblast</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>52.4</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>CSC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Capstone Copper</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>51.1</v>
+        <v>52.2</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>142.5</v>
+        <v>142.6</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>107.6</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>104.7</v>
+        <v>104.6</v>
       </c>
     </row>
     <row r="5">
@@ -1249,7 +1249,7 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="6">
@@ -1262,7 +1262,7 @@
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1301,7 +1301,7 @@
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>71.90000000000001</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="10">
@@ -1320,27 +1320,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>67.90000000000001</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>67.8</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1353,33 +1353,33 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>66.59999999999999</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>65.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>65.59999999999999</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>64.2</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="17">
@@ -1405,7 +1405,7 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="18">
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C23" t="n">
         <v>58.8</v>
@@ -1489,7 +1489,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1502,7 +1502,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1846,31 +1846,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>Deep Yellow</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-55</v>
+        <v>-55.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deep Yellow</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-54.6</v>
+        <v>-55</v>
       </c>
     </row>
     <row r="22">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.18</v>
+        <v>45.17</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.04</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.81</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37.02</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.13</v>
+        <v>33.16</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.68</v>
+        <v>27.65</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.47</v>
+        <v>26.49</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.38</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.16</v>
+        <v>22.13</v>
       </c>
     </row>
     <row r="12">

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>68.84999999999999</v>
+        <v>55.36</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>42.52</v>
+        <v>37.01</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>21.37</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>9.98</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>5.74</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>1.49</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.15</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-3.41</v>
+        <v>-3.94</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-6.74</v>
+        <v>-7.75</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-8.1</v>
+        <v>-11.07</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-24.11</v>
+        <v>-23.92</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1357.7</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>189.3</v>
+        <v>174.9</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>132.5</v>
+        <v>127.1</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>127.1</v>
+        <v>113.6</v>
       </c>
     </row>
     <row r="6">
@@ -749,47 +749,47 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>112.8</v>
+        <v>104.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>105.9</v>
+        <v>100.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>105.9</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>95.5</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="10">
@@ -829,67 +829,67 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>82.40000000000001</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>LYC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Lynas Rare Earths</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>71</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>69.09999999999999</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>69.09999999999999</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="14">
@@ -909,38 +909,38 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>69.09999999999999</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>68.2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LYC</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lynas Rare Earths</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>62.3</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="17">
@@ -969,38 +969,38 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>61.2</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mesoblast</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60.6</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AAI</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alcoa</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>60.6</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="20">
@@ -1029,38 +1029,38 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>60</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>AAI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Alcoa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>57.5</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="23">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>56.6</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>55.6</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>CSC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>Capstone Copper</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>54.7</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CSC</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capstone Copper</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>52.2</v>
+        <v>44.4</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>142.6</v>
+        <v>143.5</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>108</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>104.6</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="5">
@@ -1262,7 +1262,7 @@
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>78.2</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>77.09999999999999</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="9">
@@ -1301,7 +1301,7 @@
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>71</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="11">
@@ -1327,7 +1327,7 @@
         <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>68</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1340,33 +1340,33 @@
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>67.90000000000001</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>66.5</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>65.90000000000001</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="15">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>65.5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>64.3</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1405,7 +1405,7 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>62.9</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="18">
@@ -1418,7 +1418,7 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.5</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="19">
@@ -1431,7 +1431,7 @@
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.7</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="20">
@@ -1444,7 +1444,7 @@
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.2</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="21">
@@ -1470,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>59.4</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="23">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C23" t="n">
-        <v>58.8</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24">
@@ -1496,7 +1496,7 @@
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="25">
@@ -1509,7 +1509,7 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="26">
@@ -1522,7 +1522,7 @@
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
     </row>
   </sheetData>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-59.7</v>
+        <v>-61.1</v>
       </c>
     </row>
     <row r="13">
@@ -1756,72 +1756,72 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TWE</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Treasury Wine Estates</t>
+          <t>Deep Yellow</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-57.6</v>
+        <v>-57.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>TWE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Treasury Wine Estates</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-57.5</v>
+        <v>-57.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ARB Corporation</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-57.3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EBO</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EBOS Group</t>
+          <t>ARB Corporation</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-56.6</v>
+        <v>-57.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LLC</t>
+          <t>EBO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lendlease</t>
+          <t>EBOS Group</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1831,31 +1831,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>LLC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>Lendlease</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-55.6</v>
+        <v>-56.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deep Yellow</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-55.2</v>
+        <v>-55.6</v>
       </c>
     </row>
     <row r="21">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-52.8</v>
+        <v>-52.9</v>
       </c>
     </row>
     <row r="23">
@@ -1936,16 +1936,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>REA</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>REA Group</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-49.4</v>
+        <v>-49.6</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.62</v>
+        <v>48.67</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.17</v>
+        <v>45.16</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.07</v>
+        <v>44.11</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.87</v>
+        <v>39.96</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.99</v>
+        <v>37.01</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.16</v>
+        <v>33.21</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.65</v>
+        <v>27.67</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.49</v>
+        <v>26.52</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.4</v>
+        <v>22.41</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.13</v>
+        <v>22.11</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.83</v>
+        <v>13.84</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>55.36</v>
+        <v>53.83</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>37.01</v>
+        <v>34.01</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>18.67</v>
+        <v>18.65</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>8.029999999999999</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>4.62</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.09</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-3.94</v>
+        <v>-3.51</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-7.75</v>
+        <v>-7.64</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-11.07</v>
+        <v>-13.37</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-23.92</v>
+        <v>-23.36</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1180</v>
+        <v>1194.3</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>174.9</v>
+        <v>135.4</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>127.1</v>
+        <v>124.3</v>
       </c>
     </row>
     <row r="5">
@@ -729,18 +729,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>113.6</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -749,47 +749,47 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>104.6</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>100.8</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>82.5</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="10">
@@ -829,98 +829,98 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>71.3</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LYC</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lynas Rare Earths</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>63.5</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>62.9</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>62.2</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,18 +929,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>LYC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>Lynas Rare Earths</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>58.3</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="17">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>56.3</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="18">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>54.3</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>53.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>52.4</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AAI</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alcoa</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>51.3</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,38 +1069,38 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>51.1</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>47.8</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>46.8</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CSC</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capstone Copper</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>45.4</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>44.4</v>
+        <v>41.6</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C2" t="n">
-        <v>143.5</v>
+        <v>143.8</v>
       </c>
     </row>
     <row r="3">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C3" t="n">
         <v>108.3</v>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C4" t="n">
         <v>104.5</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C5" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
-        <v>81.7</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C7" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C8" t="n">
-        <v>77.3</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C9" t="n">
-        <v>71.90000000000001</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -1311,218 +1311,218 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C10" t="n">
-        <v>71.2</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C11" t="n">
-        <v>68.09999999999999</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C13" t="n">
-        <v>66.90000000000001</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C14" t="n">
-        <v>66.8</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C16" t="n">
-        <v>64.40000000000001</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C17" t="n">
-        <v>63.2</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C18" t="n">
-        <v>62.6</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C19" t="n">
-        <v>61.9</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C20" t="n">
-        <v>61.4</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C21" t="n">
-        <v>60.8</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>254</v>
+        <v>199</v>
       </c>
       <c r="C22" t="n">
-        <v>59.6</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>198</v>
+        <v>253</v>
       </c>
       <c r="C23" t="n">
-        <v>59</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C24" t="n">
-        <v>58.6</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>LYC</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C25" t="n">
-        <v>58.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LYC</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C26" t="n">
-        <v>57.6</v>
+        <v>57.4</v>
       </c>
     </row>
   </sheetData>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-67.2</v>
+        <v>-67</v>
       </c>
     </row>
     <row r="9">
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-65.8</v>
+        <v>-65.59999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-61.1</v>
+        <v>-61.3</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-55</v>
+        <v>-55.6</v>
       </c>
     </row>
     <row r="22">
@@ -1891,61 +1891,61 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LOV</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lovisa</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-51.5</v>
+        <v>-51.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>LOV</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Catalyst Metals</t>
+          <t>Lovisa</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-51</v>
+        <v>-51.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TNE</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TechnologyOne</t>
+          <t>Catalyst Metals</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-50.6</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>TNE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>TechnologyOne</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-49.6</v>
+        <v>-50.6</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.67</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.16</v>
+        <v>45.12</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.96</v>
+        <v>40.02</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37.01</v>
+        <v>36.92</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.21</v>
+        <v>33.14</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.67</v>
+        <v>27.62</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.52</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.41</v>
+        <v>22.39</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.11</v>
+        <v>22.06</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.84</v>
+        <v>13.85</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>53.83</v>
+        <v>53.33</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>34.01</v>
+        <v>36.11</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>18.65</v>
+        <v>19.39</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>4.38</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>2.45</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.72</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-3.51</v>
+        <v>-3.79</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-7.64</v>
+        <v>-8.279999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-13.37</v>
+        <v>-11.53</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-23.36</v>
+        <v>-24.16</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1194.3</v>
+        <v>1190.6</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>135.4</v>
+        <v>131.5</v>
       </c>
     </row>
     <row r="4">
@@ -709,78 +709,78 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>124.3</v>
+        <v>129.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>106.1</v>
+        <v>109.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>103.1</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>101.5</v>
+        <v>102.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,18 +789,18 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>82</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>81.7</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="10">
@@ -829,47 +829,47 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>72.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>66.59999999999999</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>63.9</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="13">
@@ -889,47 +889,47 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>60.6</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>56.4</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>55.6</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="16">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>54.2</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="17">
@@ -969,38 +969,38 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>51.1</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>49.9</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>49.4</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>48.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,58 +1049,58 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>44.9</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>44.7</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>44</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>43.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>42.6</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41.6</v>
+        <v>47.6</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>143.8</v>
+        <v>143.5</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>108.3</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>104.5</v>
+        <v>104.3</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="6">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
         <v>80.59999999999999</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>71.59999999999999</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>68.2</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>68.09999999999999</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>66.09999999999999</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>63.3</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="17">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C17" t="n">
         <v>62.7</v>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="19">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.5</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>60.9</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>59.7</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C22" t="n">
-        <v>59</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="23">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>58.7</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="24">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>58.5</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="25">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="26">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
     </row>
   </sheetData>
@@ -1876,31 +1876,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-52.9</v>
+        <v>-54.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-51.7</v>
+        <v>-52.9</v>
       </c>
     </row>
     <row r="24">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.65</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.12</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>43.96</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.02</v>
+        <v>40.01</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.92</v>
+        <v>36.88</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.14</v>
+        <v>33.09</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.62</v>
+        <v>27.61</v>
       </c>
     </row>
     <row r="9">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.39</v>
+        <v>22.36</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.06</v>
+        <v>22.04</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.85</v>
+        <v>13.86</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>53.33</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>36.11</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>19.39</v>
+        <v>19.13</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>8.81</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>1.34</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.15</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-3.79</v>
+        <v>-5.05</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-8.279999999999999</v>
+        <v>-8.42</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-11.53</v>
+        <v>-12.17</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-24.16</v>
+        <v>-24.08</v>
       </c>
     </row>
   </sheetData>
@@ -669,47 +669,47 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1190.6</v>
+        <v>1229.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>131.5</v>
+        <v>128.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>129.2</v>
+        <v>121.3</v>
       </c>
     </row>
     <row r="5">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>108</v>
+        <v>109.4</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>102.3</v>
+        <v>106.9</v>
       </c>
     </row>
     <row r="8">
@@ -789,47 +789,47 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>90.3</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>75.7</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>73.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -849,38 +849,38 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>68.7</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>67.3</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,58 +889,58 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>64.5</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>58.7</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>57.8</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LYC</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lynas Rare Earths</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,18 +949,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>57.6</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,38 +969,38 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>54.9</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>LYC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Lynas Rare Earths</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>50.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>50</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,27 +1049,27 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>49.2</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="23">
@@ -1089,38 +1089,38 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>48.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>48</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>48</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="26">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>47.6</v>
+        <v>48.5</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>143.5</v>
+        <v>143.4</v>
       </c>
     </row>
     <row r="3">
@@ -1262,7 +1262,7 @@
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>80.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>78.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>77.09999999999999</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9">
@@ -1301,7 +1301,7 @@
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>71.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>66.90000000000001</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="14">
@@ -1366,7 +1366,7 @@
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="15">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>63.9</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="16">
@@ -1405,7 +1405,7 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>62.7</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="18">
@@ -1431,7 +1431,7 @@
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.4</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="20">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>59.8</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C22" t="n">
-        <v>58.8</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="23">
@@ -1496,7 +1496,7 @@
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>58.4</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="25">
@@ -1509,7 +1509,7 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.6</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="26">
@@ -1846,31 +1846,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-55.6</v>
+        <v>-56.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-55.6</v>
+        <v>-55.9</v>
       </c>
     </row>
     <row r="22">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.6</v>
+        <v>48.64</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.06</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="4">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.01</v>
+        <v>40.08</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.88</v>
+        <v>36.89</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.09</v>
+        <v>33.11</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.61</v>
+        <v>27.63</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.5</v>
+        <v>26.52</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.36</v>
+        <v>22.39</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.04</v>
+        <v>22.06</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.86</v>
+        <v>13.89</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>54.93</v>
+        <v>52.46</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>35.9</v>
+        <v>36.06</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>19.13</v>
+        <v>18.35</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>10.39</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.09</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.05</v>
+        <v>-5.24</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-8.42</v>
+        <v>-10.14</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-12.17</v>
+        <v>-14.43</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-24.08</v>
+        <v>-25.17</v>
       </c>
     </row>
   </sheetData>
@@ -669,47 +669,47 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1229.4</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>128.9</v>
+        <v>131.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>121.3</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>109.4</v>
+        <v>119.5</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>109.4</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>106.9</v>
+        <v>102.9</v>
       </c>
     </row>
     <row r="8">
@@ -789,38 +789,38 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>92.5</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>75.5</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,38 +829,38 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>73.40000000000001</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>67.5</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="13">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>62.8</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="14">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>60.8</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="15">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>60.4</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="16">
@@ -949,18 +949,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>57.9</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,38 +969,38 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LYC</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lynas Rare Earths</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,38 +1009,38 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>52</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>51.8</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>49.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>LYC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Lynas Rare Earths</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,38 +1089,38 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>49.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>48.9</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>CSC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>Capstone Copper</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>48.5</v>
+        <v>46.7</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>143.4</v>
+        <v>143.5</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>108.2</v>
+        <v>108.1</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>104.3</v>
+        <v>104.2</v>
       </c>
     </row>
     <row r="5">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>77</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="9">
@@ -1314,13 +1314,13 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>71.5</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1333,14 +1333,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="13">
@@ -1372,115 +1372,115 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>63.7</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>63.4</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>62.9</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>61.9</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>60.8</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>59.9</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>201</v>
+        <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>58.7</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>254</v>
+        <v>202</v>
       </c>
       <c r="C23" t="n">
         <v>58.6</v>
@@ -1496,7 +1496,7 @@
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>58.3</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="25">
@@ -1522,7 +1522,7 @@
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.5</v>
+        <v>57.3</v>
       </c>
     </row>
   </sheetData>
@@ -1675,67 +1675,67 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-67</v>
+        <v>-66.59999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Telix Pharmaceuticals</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-65.59999999999999</v>
+        <v>-65.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>XRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>Xero</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-65.3</v>
+        <v>-64.40000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XRO</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Xero</t>
+          <t>Austal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-64.09999999999999</v>
+        <v>-61.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Austal</t>
+          <t>Telix Pharmaceuticals</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-61.3</v>
+        <v>-59.5</v>
       </c>
     </row>
     <row r="13">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.08</v>
+        <v>45.12</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43.96</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.08</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.89</v>
+        <v>36.86</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.11</v>
+        <v>33.13</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.63</v>
+        <v>27.68</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.52</v>
+        <v>26.54</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.39</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="11">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.89</v>
+        <v>13.91</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>52.46</v>
+        <v>44.95</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>36.06</v>
+        <v>31.64</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>18.35</v>
+        <v>17.43</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>12.74</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>4.66</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>2.05</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.79</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.24</v>
+        <v>-5.15</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-10.14</v>
+        <v>-10.8</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-14.43</v>
+        <v>-17.04</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.17</v>
+        <v>-25.78</v>
       </c>
     </row>
   </sheetData>
@@ -669,47 +669,47 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1196</v>
+        <v>1096.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>131.1</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>128.7</v>
+        <v>118.5</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>119.5</v>
+        <v>106.9</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>106.1</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>102.9</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
@@ -789,18 +789,18 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>95.7</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -809,18 +809,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>78.8</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,38 +829,38 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>71.8</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>69.59999999999999</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,78 +869,78 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>66.5</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>62.1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>59.3</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>58.4</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,38 +949,38 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>53.5</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>53.2</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>52.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,38 +1009,38 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>50.9</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>50.4</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,38 +1049,38 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>49.8</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>49</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LYC</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lynas Rare Earths</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>49</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>48.5</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>47.1</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="26">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>46.7</v>
+        <v>40.9</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>143.5</v>
+        <v>143.6</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>108.1</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>104.2</v>
+        <v>104.3</v>
       </c>
     </row>
     <row r="5">
@@ -1262,7 +1262,7 @@
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>80.40000000000001</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="8">
@@ -1301,7 +1301,7 @@
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72.09999999999999</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="10">
@@ -1314,33 +1314,33 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>71.7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>68.3</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>68.2</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>66.8</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1366,7 +1366,7 @@
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>66.3</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="15">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>65.8</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16">
@@ -1405,7 +1405,7 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>63.4</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="18">
@@ -1418,7 +1418,7 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.9</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
@@ -1431,7 +1431,7 @@
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.9</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="20">
@@ -1444,7 +1444,7 @@
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.3</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>61.1</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="22">
@@ -1470,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>59.9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C23" t="n">
-        <v>58.6</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="24">
@@ -1496,7 +1496,7 @@
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>58.1</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="25">
@@ -1509,20 +1509,20 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.8</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
     </row>
   </sheetData>
@@ -1675,37 +1675,37 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-66.59999999999999</v>
+        <v>-66.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>XRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>Xero</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-65.3</v>
+        <v>-66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XRO</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Xero</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-64.40000000000001</v>
+        <v>-65.3</v>
       </c>
     </row>
     <row r="11">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-59.5</v>
+        <v>-59.4</v>
       </c>
     </row>
     <row r="13">
@@ -1801,42 +1801,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ARB Corporation</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-57.3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EBO</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EBOS Group</t>
+          <t>ARB Corporation</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-56.6</v>
+        <v>-57.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LLC</t>
+          <t>EBO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lendlease</t>
+          <t>EBOS Group</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1846,12 +1846,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>LLC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>Lendlease</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-54.2</v>
+        <v>-55.1</v>
       </c>
     </row>
     <row r="23">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-52.9</v>
+        <v>-54.3</v>
       </c>
     </row>
     <row r="24">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.64</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.12</v>
+        <v>45.18</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43.95</v>
+        <v>43.96</v>
       </c>
     </row>
     <row r="5">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.86</v>
+        <v>36.79</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.13</v>
+        <v>33.11</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.68</v>
+        <v>27.71</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.54</v>
+        <v>26.56</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.4</v>
+        <v>22.39</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.06</v>
+        <v>22.08</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.91</v>
+        <v>13.9</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>44.95</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>31.64</v>
+        <v>40.29</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>17.43</v>
+        <v>20.45</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>12.4</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>4.01</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>1.14</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.27</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.15</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-10.8</v>
+        <v>-10.71</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-17.04</v>
+        <v>-15.37</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.78</v>
+        <v>-25.53</v>
       </c>
     </row>
   </sheetData>
@@ -669,58 +669,58 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1096.2</v>
+        <v>1266.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>128</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>118.5</v>
+        <v>140.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,58 +729,58 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>106.9</v>
+        <v>136.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>94.8</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>90</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>86.8</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>70.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>66.8</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>64.8</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,38 +869,38 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>62.1</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,38 +909,38 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>58.3</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>57.1</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,78 +949,78 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>53.6</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>50.6</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>47.9</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>47.7</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,38 +1049,38 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>47.4</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>46.5</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>43.5</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>43.3</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41.3</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CSC</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capstone Copper</t>
+          <t>Capricorn Metals</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>40.9</v>
+        <v>51.9</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C2" t="n">
-        <v>143.6</v>
+        <v>143.7</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C3" t="n">
-        <v>108.2</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C4" t="n">
-        <v>104.3</v>
+        <v>104.1</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C5" t="n">
-        <v>81.7</v>
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
-        <v>80.7</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C7" t="n">
-        <v>78.7</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C8" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C9" t="n">
-        <v>72.3</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C10" t="n">
-        <v>72</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C11" t="n">
-        <v>68.5</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C12" t="n">
-        <v>68.40000000000001</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C13" t="n">
-        <v>67.09999999999999</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C14" t="n">
-        <v>66.5</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C15" t="n">
         <v>66</v>
@@ -1385,40 +1385,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C16" t="n">
-        <v>63.6</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C17" t="n">
-        <v>63.6</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="19">
@@ -1428,36 +1428,36 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C19" t="n">
-        <v>62.3</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C20" t="n">
-        <v>61.6</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C21" t="n">
-        <v>61.3</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="22">
@@ -1467,33 +1467,33 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C22" t="n">
-        <v>60</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>203</v>
+        <v>253</v>
       </c>
       <c r="C23" t="n">
-        <v>58.5</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>254</v>
+        <v>204</v>
       </c>
       <c r="C24" t="n">
         <v>58.3</v>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C25" t="n">
-        <v>57.7</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="26">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C26" t="n">
-        <v>57.2</v>
+        <v>57.3</v>
       </c>
     </row>
   </sheetData>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-59.4</v>
+        <v>-59.1</v>
       </c>
     </row>
     <row r="13">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.6</v>
+        <v>48.57</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.18</v>
+        <v>45.23</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43.96</v>
+        <v>43.97</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.1</v>
+        <v>40.11</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.79</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.11</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.71</v>
+        <v>27.77</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.56</v>
+        <v>26.62</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.39</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.08</v>
+        <v>22.12</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.9</v>
+        <v>13.91</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>55.67</v>
+        <v>55.72</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>40.29</v>
+        <v>37.93</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>20.45</v>
+        <v>19.31</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>11.69</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>4.25</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>1.66</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.61</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.25</v>
+        <v>-2.93</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-10.71</v>
+        <v>-7.97</v>
       </c>
     </row>
     <row r="11">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.53</v>
+        <v>-23.56</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1266.7</v>
+        <v>1254.2</v>
       </c>
     </row>
     <row r="3">
@@ -689,18 +689,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>150</v>
+        <v>137.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,18 +709,18 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>140.3</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>136.6</v>
+        <v>122.3</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>108.9</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="7">
@@ -769,18 +769,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>99.09999999999999</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,18 +789,18 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>86.40000000000001</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="10">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>80.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>75.09999999999999</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="12">
@@ -869,47 +869,47 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>67.2</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>66.3</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>64.40000000000001</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="15">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>62.4</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="16">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>62.4</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="17">
@@ -969,58 +969,58 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>59.7</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>58.6</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>58.1</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>55.3</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>55.2</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>54.4</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>54.3</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,27 +1109,27 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>52.6</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>52.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="26">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>51.9</v>
+        <v>50.5</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>143.7</v>
+        <v>143.5</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>108.6</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>104.1</v>
+        <v>104.7</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>81.90000000000001</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>80.5</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>77.5</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C9" t="n">
         <v>72.5</v>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>71.59999999999999</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>68.90000000000001</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>67.3</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>66.40000000000001</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="17">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C17" t="n">
         <v>63.1</v>
@@ -1415,36 +1415,36 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.6</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>62.4</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.8</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>61.7</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>60.6</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="23">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="24">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C24" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="25">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.8</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="26">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.57</v>
+        <v>48.52</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.23</v>
+        <v>45.21</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43.97</v>
+        <v>43.93</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.11</v>
+        <v>40.12</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.7</v>
+        <v>36.65</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.07</v>
+        <v>33.05</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.77</v>
+        <v>27.75</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.62</v>
+        <v>26.65</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.4</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="11">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.91</v>
+        <v>13.89</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>55.72</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>37.93</v>
+        <v>39.61</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>19.31</v>
+        <v>18.97</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>12.01</v>
+        <v>14.49</v>
       </c>
     </row>
     <row r="6">
@@ -517,33 +517,33 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>4.56</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>2.36</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-2.93</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-7.97</v>
+        <v>-4.82</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-15.37</v>
+        <v>-15.02</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-23.56</v>
+        <v>-22.24</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1254.2</v>
+        <v>1287.2</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>137.6</v>
+        <v>144.8</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>129.1</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>122.3</v>
+        <v>112.4</v>
       </c>
     </row>
     <row r="6">
@@ -749,38 +749,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>106.5</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>92.7</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,27 +789,27 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>83</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>81.3</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="10">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75.59999999999999</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,58 +849,58 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>67.7</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>64.90000000000001</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>64.90000000000001</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,18 +909,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>62.1</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,18 +929,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>59.5</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,67 +949,67 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>58.2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>57.9</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>57.7</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>57.1</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="20">
@@ -1035,12 +1035,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,38 +1049,38 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>54</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>53.5</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,67 +1089,67 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>53.3</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>50.6</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>50.6</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capricorn Metals</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>50.5</v>
+        <v>51.5</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>143.5</v>
+        <v>143.4</v>
       </c>
     </row>
     <row r="3">
@@ -1249,7 +1249,7 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1262,7 +1262,7 @@
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>80.3</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>78.90000000000001</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>77.40000000000001</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="9">
@@ -1301,7 +1301,7 @@
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>71.5</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1327,7 +1327,7 @@
         <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>68.8</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1340,72 +1340,72 @@
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>68.59999999999999</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>67.2</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>66.5</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>65.90000000000001</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>63.6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>63.1</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="18">
@@ -1470,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>60.5</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="23">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C24" t="n">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="25">
@@ -1509,7 +1509,7 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.7</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="26">
@@ -1522,7 +1522,7 @@
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.2</v>
+        <v>57.3</v>
       </c>
     </row>
   </sheetData>
@@ -1576,27 +1576,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>TUA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wisetech Global</t>
+          <t>Tuas</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-76.09999999999999</v>
+        <v>-76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TUA</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tuas</t>
+          <t>Wisetech Global</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-59.1</v>
+        <v>-59</v>
       </c>
     </row>
     <row r="13">
@@ -1756,57 +1756,57 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deep Yellow</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-57.7</v>
+        <v>-58.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TWE</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Treasury Wine Estates</t>
+          <t>Deep Yellow</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-57.6</v>
+        <v>-57.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>TWE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Treasury Wine Estates</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-57.5</v>
+        <v>-57.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1816,42 +1816,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ARB Corporation</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-57.3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EBO</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EBOS Group</t>
+          <t>ARB Corporation</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-56.6</v>
+        <v>-57.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LLC</t>
+          <t>EBO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lendlease</t>
+          <t>EBOS Group</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1861,31 +1861,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>LLC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>Lendlease</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-55.9</v>
+        <v>-56.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-55.1</v>
+        <v>-55.9</v>
       </c>
     </row>
     <row r="23">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.52</v>
+        <v>48.58</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.21</v>
+        <v>45.28</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43.93</v>
+        <v>44.02</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.12</v>
+        <v>40.19</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.65</v>
+        <v>36.73</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.05</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.75</v>
+        <v>27.79</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.65</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.38</v>
+        <v>22.41</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.12</v>
+        <v>22.15</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.89</v>
+        <v>13.92</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>59.47</v>
+        <v>55.98</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>39.61</v>
+        <v>35.11</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>18.97</v>
+        <v>16.29</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>14.49</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="6">
@@ -517,33 +517,33 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>4.74</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>2.82</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>2.39</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.34</v>
+        <v>-4.39</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-4.82</v>
+        <v>-6.58</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-15.02</v>
+        <v>-15.01</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-22.24</v>
+        <v>-22.62</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1287.2</v>
+        <v>1237.5</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>144.8</v>
+        <v>144.1</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>112.4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -749,38 +749,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>103.2</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>95.2</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,38 +789,38 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>90.8</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>89.3</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>84.8</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>82.8</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="12">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>69.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>66.8</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,18 +909,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>61.9</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,18 +929,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>61.3</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,58 +949,58 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>58</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>57.7</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>56.5</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,38 +1009,38 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>56.4</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>55.2</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,78 +1049,78 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>55.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>54.9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>54.8</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>53.7</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>53.4</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>51.5</v>
+        <v>46.8</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>143.4</v>
+        <v>143.5</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>108.7</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>104.7</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="5">
@@ -1262,7 +1262,7 @@
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>80.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>77.5</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1301,7 +1301,7 @@
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72.40000000000001</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="10">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>71.40000000000001</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="11">
@@ -1327,7 +1327,7 @@
         <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>68.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>66.3</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="14">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>63.6</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="16">
@@ -1398,14 +1398,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>62.8</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="18">
@@ -1424,14 +1424,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>62.3</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="20">
@@ -1444,7 +1444,7 @@
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>62.3</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>61.9</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="22">
@@ -1470,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>60.8</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23">
@@ -1483,7 +1483,7 @@
         <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="24">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C24" t="n">
-        <v>58.1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25">
@@ -1509,7 +1509,7 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.8</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="26">
@@ -1522,7 +1522,7 @@
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.3</v>
+        <v>57.5</v>
       </c>
     </row>
   </sheetData>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-76</v>
+        <v>-75.8</v>
       </c>
     </row>
     <row r="4">
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-71.3</v>
+        <v>-71.2</v>
       </c>
     </row>
     <row r="6">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-66.5</v>
+        <v>-66.40000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1705,67 +1705,67 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-65.3</v>
+        <v>-65.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Austal</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-61.3</v>
+        <v>-62.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Telix Pharmaceuticals</t>
+          <t>Austal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-59</v>
+        <v>-61.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Seek</t>
+          <t>Telix Pharmaceuticals</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-58.7</v>
+        <v>-59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>Seek</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-58.1</v>
+        <v>-58.7</v>
       </c>
     </row>
     <row r="15">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-57.7</v>
+        <v>-58.2</v>
       </c>
     </row>
     <row r="16">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.58</v>
+        <v>48.61</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.28</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.02</v>
+        <v>44.04</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.19</v>
+        <v>40.21</v>
       </c>
     </row>
     <row r="6">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.1</v>
+        <v>33.11</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.79</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.7</v>
+        <v>26.71</v>
       </c>
     </row>
     <row r="10">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.15</v>
+        <v>22.17</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.92</v>
+        <v>13.95</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>55.98</v>
+        <v>66.31</v>
       </c>
     </row>
     <row r="3">
@@ -478,33 +478,33 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>35.11</v>
+        <v>41.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>16.29</v>
+        <v>17.88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>14.28</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>3.07</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>1.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.59</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.39</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-6.58</v>
+        <v>-6.69</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-15.01</v>
+        <v>-15.08</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-22.62</v>
+        <v>-23.9</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1237.5</v>
+        <v>1412.5</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>144.1</v>
+        <v>158.6</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>120</v>
+        <v>124.1</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>100</v>
+        <v>108.4</v>
       </c>
     </row>
     <row r="6">
@@ -749,58 +749,58 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>95.5</v>
+        <v>103.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>88.2</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>87.8</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -809,18 +809,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>76.5</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>76.3</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="11">
@@ -849,38 +849,38 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>74.2</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>69.09999999999999</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>66.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -909,38 +909,38 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>60.5</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>54.8</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>54.1</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="17">
@@ -969,38 +969,38 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>53.2</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>CSC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Capstone Copper</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>52</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,98 +1009,98 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>51.6</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>51.5</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>51</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>51</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>50.2</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,38 +1109,38 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>47.9</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>47.2</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>46.8</v>
+        <v>55.1</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>143.5</v>
+        <v>143.9</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>109</v>
+        <v>109.3</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>104.5</v>
+        <v>102.9</v>
       </c>
     </row>
     <row r="5">
@@ -1249,7 +1249,7 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="6">
@@ -1262,7 +1262,7 @@
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>81.40000000000001</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>78.7</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>77.59999999999999</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>71.5</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1327,7 +1327,7 @@
         <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>69.09999999999999</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="12">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>66.2</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="14">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>63.8</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="16">
@@ -1405,20 +1405,20 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>62.7</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.7</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="19">
@@ -1431,20 +1431,20 @@
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>62.7</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>62.6</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>61.7</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="22">
@@ -1483,7 +1483,7 @@
         <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>58.6</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="24">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C24" t="n">
-        <v>58</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="25">
@@ -1509,7 +1509,7 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.9</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="26">
@@ -1522,7 +1522,7 @@
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.5</v>
+        <v>57.4</v>
       </c>
     </row>
   </sheetData>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-74</v>
+        <v>-74.3</v>
       </c>
     </row>
     <row r="5">
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-62.7</v>
+        <v>-63.4</v>
       </c>
     </row>
     <row r="12">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.61</v>
+        <v>48.69</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.36</v>
+        <v>45.43</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.04</v>
+        <v>44.08</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.21</v>
+        <v>40.27</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.73</v>
+        <v>36.72</v>
       </c>
     </row>
     <row r="7">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.8</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.71</v>
+        <v>26.74</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.41</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.17</v>
+        <v>22.18</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.95</v>
+        <v>13.96</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>66.31</v>
+        <v>42.44</v>
       </c>
     </row>
     <row r="3">
@@ -478,33 +478,33 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>41.88</v>
+        <v>40.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>17.88</v>
+        <v>20.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>16.66</v>
+        <v>17.43</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>2.96</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.29</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.27</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-6.69</v>
+        <v>-5.13</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-15.08</v>
+        <v>-12.9</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-23.9</v>
+        <v>-23.32</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1412.5</v>
+        <v>1015.5</v>
       </c>
     </row>
     <row r="3">
@@ -689,18 +689,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>158.6</v>
+        <v>142.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,18 +709,18 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>124.1</v>
+        <v>135.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,38 +729,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>108.4</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>103.9</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -769,38 +769,38 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>102.8</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>93.40000000000001</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -815,12 +815,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>86.3</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>86</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,18 +869,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>78.09999999999999</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>74.59999999999999</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>70.59999999999999</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="15">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>69.2</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16">
@@ -955,12 +955,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -975,12 +975,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CSC</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capstone Copper</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,27 +989,27 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>59.9</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>59.7</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="20">
@@ -1029,38 +1029,38 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>59.2</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>56.6</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1075,12 +1075,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>56.2</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,38 +1109,38 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>55.6</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>55.4</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>55.1</v>
+        <v>53.3</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C2" t="n">
-        <v>143.9</v>
+        <v>141.3</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C3" t="n">
-        <v>109.3</v>
+        <v>109.4</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C4" t="n">
-        <v>102.9</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C5" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C7" t="n">
-        <v>78.2</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C8" t="n">
-        <v>78</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C9" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C10" t="n">
-        <v>71.90000000000001</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C11" t="n">
-        <v>69.2</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C12" t="n">
-        <v>68.7</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C13" t="n">
-        <v>66.5</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C14" t="n">
-        <v>65.90000000000001</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C15" t="n">
         <v>63.7</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="17">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C17" t="n">
-        <v>62.8</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="18">
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C18" t="n">
         <v>62.5</v>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C19" t="n">
         <v>62.5</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C20" t="n">
         <v>62.3</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C21" t="n">
-        <v>61.5</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C22" t="n">
-        <v>61</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="23">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C23" t="n">
-        <v>58.8</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="24">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C24" t="n">
-        <v>57.9</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="25">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C25" t="n">
-        <v>57.8</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="26">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C26" t="n">
-        <v>57.4</v>
+        <v>57.2</v>
       </c>
     </row>
   </sheetData>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-75.8</v>
+        <v>-75.3</v>
       </c>
     </row>
     <row r="4">
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-71.2</v>
+        <v>-70.8</v>
       </c>
     </row>
     <row r="6">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-66.40000000000001</v>
+        <v>-66.2</v>
       </c>
     </row>
     <row r="9">
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-66</v>
+        <v>-65.59999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1741,72 +1741,72 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Telix Pharmaceuticals</t>
+          <t>Seek</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-59</v>
+        <v>-58.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Seek</t>
+          <t>Deep Yellow</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-58.7</v>
+        <v>-58.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>TWE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deep Yellow</t>
+          <t>Treasury Wine Estates</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-58.2</v>
+        <v>-57.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TWE</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Treasury Wine Estates</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-57.6</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1816,16 +1816,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>Telix Pharmaceuticals</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-57.5</v>
+        <v>-57.4</v>
       </c>
     </row>
     <row r="19">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.69</v>
+        <v>48.71</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.43</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="4">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.27</v>
+        <v>40.33</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.72</v>
+        <v>36.62</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.11</v>
+        <v>33.09</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.78</v>
+        <v>27.75</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.74</v>
+        <v>26.73</v>
       </c>
     </row>
     <row r="10">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.18</v>
+        <v>22.21</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.96</v>
+        <v>13.97</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>42.44</v>
+        <v>49.37</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>40.49</v>
+        <v>43.51</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>20.02</v>
+        <v>22.04</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>17.43</v>
+        <v>17.71</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>4.24</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>2.27</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="8">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-3.87</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-5.13</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-12.9</v>
+        <v>-10.29</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-23.32</v>
+        <v>-22.07</v>
       </c>
     </row>
   </sheetData>
@@ -669,47 +669,47 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1015.5</v>
+        <v>1111.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>142.1</v>
+        <v>156.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>135.3</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5">
@@ -729,27 +729,27 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>128.7</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>92.3</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -769,18 +769,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>91.90000000000001</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,38 +789,38 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>91.3</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>87.7</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>85.8</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>84.90000000000001</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>80.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>77.2</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>75.5</v>
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>75</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>62.6</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="17">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>60.1</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,38 +989,38 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>59.8</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>58.8</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,27 +1029,27 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>58.7</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>57.7</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="22">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>56.5</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="23">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>55.1</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>55</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>54.7</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>CSC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Capstone Copper</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>53.3</v>
+        <v>56.3</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>141.3</v>
+        <v>141.2</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>109.4</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>103.3</v>
+        <v>104.1</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="6">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
         <v>81.3</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>78.40000000000001</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="8">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
         <v>78.09999999999999</v>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="10">
@@ -1311,36 +1311,36 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>72</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>68.8</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>66.59999999999999</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="14">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" t="n">
         <v>66</v>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>63.1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C17" t="n">
         <v>62.9</v>
@@ -1411,11 +1411,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C18" t="n">
         <v>62.5</v>
@@ -1424,14 +1424,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>62.5</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>62.3</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>61.6</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>60.6</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="23">
@@ -1480,33 +1480,33 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>58.9</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>LYC</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>209</v>
+        <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>57.8</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LYC</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>253</v>
+        <v>210</v>
       </c>
       <c r="C25" t="n">
         <v>57.7</v>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.2</v>
+        <v>57.1</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.71</v>
+        <v>48.69</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.42</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.08</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.33</v>
+        <v>40.31</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.62</v>
+        <v>36.59</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.09</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.75</v>
+        <v>27.74</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.73</v>
+        <v>26.71</v>
       </c>
     </row>
     <row r="10">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.21</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.97</v>
+        <v>13.96</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>49.37</v>
+        <v>61.87</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>43.51</v>
+        <v>46.86</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>22.04</v>
+        <v>19.09</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>17.71</v>
+        <v>17.19</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>5.92</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>1.91</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>1.18</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-2.57</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-5.33</v>
+        <v>-5.51</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-10.29</v>
+        <v>-10.57</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-22.07</v>
+        <v>-22.57</v>
       </c>
     </row>
   </sheetData>
@@ -669,67 +669,67 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1111.3</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>156.3</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>154</v>
+        <v>131.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>130</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="6">
@@ -749,18 +749,18 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>96.59999999999999</v>
+        <v>106.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -769,18 +769,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>94.3</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,38 +789,38 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>93</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>92.40000000000001</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,38 +829,38 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>88.8</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>87.2</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>82.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -889,67 +889,67 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>81</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>79.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>77.40000000000001</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>67.2</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="17">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>63.6</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,38 +989,38 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>61.4</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,38 +1029,38 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>59.2</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>58.8</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>58.3</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,27 +1089,27 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>58.2</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>57.6</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="25">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>56.6</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CSC</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capstone Copper</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>56.3</v>
+        <v>61.4</v>
       </c>
     </row>
   </sheetData>
@@ -1210,33 +1210,33 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>141.2</v>
+        <v>141.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>DRO</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>109.5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DRO</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>104.1</v>
+        <v>100.8</v>
       </c>
     </row>
     <row r="5">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>78.2</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>78.09999999999999</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="9">
@@ -1301,7 +1301,7 @@
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72.3</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="10">
@@ -1314,33 +1314,33 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>71.90000000000001</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>69.59999999999999</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>69.2</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="13">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>66.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="14">
@@ -1366,7 +1366,7 @@
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="15">
@@ -1379,46 +1379,46 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>63.6</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>62.9</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.5</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="19">
@@ -1431,7 +1431,7 @@
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>62.4</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="20">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>61.5</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="22">
@@ -1470,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>60.5</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23">
@@ -1483,7 +1483,7 @@
         <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>59</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="24">
@@ -1496,7 +1496,7 @@
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>58</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="25">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C25" t="n">
-        <v>57.7</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="26">
@@ -1522,7 +1522,7 @@
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.1</v>
+        <v>57.6</v>
       </c>
     </row>
   </sheetData>
@@ -1816,42 +1816,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Telix Pharmaceuticals</t>
+          <t>ARB Corporation</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-57.4</v>
+        <v>-57.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>EBO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ARB Corporation</t>
+          <t>EBOS Group</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-57.3</v>
+        <v>-56.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EBO</t>
+          <t>LLC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EBOS Group</t>
+          <t>Lendlease</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1861,31 +1861,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LLC</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lendlease</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-56.6</v>
+        <v>-55.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>Telix Pharmaceuticals</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-55.9</v>
+        <v>-54.4</v>
       </c>
     </row>
     <row r="23">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.69</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.4</v>
+        <v>45.49</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.1</v>
+        <v>44.17</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.31</v>
+        <v>40.38</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.59</v>
+        <v>36.63</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.07</v>
+        <v>33.06</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.74</v>
+        <v>27.79</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.71</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.4</v>
+        <v>22.42</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.2</v>
+        <v>22.23</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.96</v>
+        <v>13.99</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>61.87</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>46.86</v>
+        <v>46.93</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>19.09</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>17.19</v>
+        <v>15.74</v>
       </c>
     </row>
     <row r="6">
@@ -517,33 +517,33 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>5.37</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>0.93</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.49</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-3.54</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-5.51</v>
+        <v>-4.87</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-10.57</v>
+        <v>-12.07</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-22.57</v>
+        <v>-22.33</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1309</v>
+        <v>1074.7</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>154</v>
+        <v>152.2</v>
       </c>
     </row>
     <row r="4">
@@ -709,18 +709,18 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>131.5</v>
+        <v>125.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,18 +729,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>106.7</v>
+        <v>114.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>106.3</v>
+        <v>113.4</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>97</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>94.59999999999999</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -809,18 +809,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>92.5</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -835,32 +835,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>86.3</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,67 +869,67 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>84.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>83.8</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>80.90000000000001</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>75.2</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="16">
@@ -949,18 +949,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>75.2</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>71.2</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>67.59999999999999</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="19">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>66.40000000000001</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>64.40000000000001</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>64.3</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>63.7</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,27 +1089,27 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>62.2</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="25">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>61.9</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>61.4</v>
+        <v>60.8</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>141.3</v>
+        <v>140.4</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>104</v>
+        <v>104.1</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>100.8</v>
+        <v>100.7</v>
       </c>
     </row>
     <row r="5">
@@ -1288,39 +1288,39 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72.2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>72</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1333,14 +1333,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>69.7</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="13">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>64.09999999999999</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="16">
@@ -1405,46 +1405,46 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>62.8</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.6</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>62.5</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>62.4</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>61.7</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="22">
@@ -1502,27 +1502,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>211</v>
+        <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.8</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>254</v>
+        <v>212</v>
       </c>
       <c r="C26" t="n">
-        <v>57.6</v>
+        <v>57.7</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.76</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.49</v>
+        <v>45.46</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.17</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.38</v>
+        <v>40.39</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.63</v>
+        <v>36.59</v>
       </c>
     </row>
     <row r="7">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.79</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.77</v>
+        <v>26.81</v>
       </c>
     </row>
     <row r="10">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.23</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.99</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -458,27 +458,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>47.32</v>
+        <v>49.37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>46.93</v>
+        <v>29.88</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>18.05</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>15.74</v>
+        <v>15.61</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>4.89</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.26</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.5</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-4.87</v>
+        <v>-5.74</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-12.07</v>
+        <v>-12.28</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-22.33</v>
+        <v>-22.37</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +625,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1074.7</v>
+        <v>788.4</v>
       </c>
     </row>
     <row r="3">
@@ -689,47 +689,47 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>152.2</v>
+        <v>158.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>125.7</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>114.3</v>
+        <v>122.3</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>113.4</v>
+        <v>116.9</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>98.7</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -789,18 +789,18 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>93.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -809,18 +809,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>89</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>86.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>85.40000000000001</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -869,38 +869,38 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>82.40000000000001</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>80</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,78 +909,78 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>78.59999999999999</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>75.5</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>73.5</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>72.59999999999999</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>70.2</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>69.3</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>68.2</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>67.5</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>67.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>64</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="25">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>60.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>60.8</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>140.4</v>
+        <v>139.5</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>104.1</v>
+        <v>104.2</v>
       </c>
     </row>
     <row r="4">
@@ -1236,33 +1236,33 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>100.7</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TUA</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>81.5</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>TUA</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>81.3</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="7">
@@ -1340,7 +1340,7 @@
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>69.5</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="13">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>64.2</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>63.1</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="17">
@@ -1418,7 +1418,7 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.4</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="19">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C19" t="n">
-        <v>62.3</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="20">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>61.6</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="22">
@@ -1470,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>61</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="23">
@@ -1483,7 +1483,7 @@
         <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="24">
@@ -1509,20 +1509,20 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.7</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>212</v>
+        <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.82</v>
+        <v>48.87</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.46</v>
+        <v>45.51</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.19</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.39</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="6">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.06</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="8">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.42</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="11">

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>49.37</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="3">
@@ -478,33 +478,33 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>29.88</v>
+        <v>33.55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>16.5</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>15.61</v>
+        <v>15.52</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>4.48</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>1.24</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="8">
@@ -543,33 +543,33 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.6</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.6</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>-5.74</v>
+        <v>-4.98</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-12.28</v>
+        <v>-12.19</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-22.37</v>
+        <v>-21.43</v>
       </c>
     </row>
   </sheetData>
@@ -669,18 +669,18 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>788.4</v>
+        <v>816.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -689,18 +689,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>158.8</v>
+        <v>141.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>127.2</v>
+        <v>123.6</v>
       </c>
     </row>
     <row r="5">
@@ -729,18 +729,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>122.3</v>
+        <v>119.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -749,18 +749,18 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>116.9</v>
+        <v>104.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -769,18 +769,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>97.09999999999999</v>
+        <v>102.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,18 +789,18 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>95.59999999999999</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -809,18 +809,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>92.90000000000001</v>
+        <v>85.59999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>86.09999999999999</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>84.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,18 +869,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>84.2</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>83.3</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,38 +909,38 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>77.8</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>77.40000000000001</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>75.59999999999999</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>75.2</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>73.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>71.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,38 +1029,38 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>70.2</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>68.90000000000001</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Capricorn Metals</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>64.90000000000001</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61.8</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>61</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>60.8</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C2" t="n">
-        <v>139.5</v>
+        <v>138.8</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C3" t="n">
-        <v>104.2</v>
+        <v>104.3</v>
       </c>
     </row>
     <row r="4">
@@ -1233,36 +1233,36 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C4" t="n">
-        <v>100.2</v>
+        <v>100.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>TUA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C5" t="n">
-        <v>81.8</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TUA</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
-        <v>81.5</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C7" t="n">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C8" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C9" t="n">
-        <v>72</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C10" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C11" t="n">
-        <v>69.7</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C12" t="n">
-        <v>69.3</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C13" t="n">
-        <v>66.7</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C14" t="n">
-        <v>65.8</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C15" t="n">
-        <v>64.40000000000001</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C16" t="n">
-        <v>63.3</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="17">
@@ -1402,23 +1402,23 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C17" t="n">
-        <v>62.9</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C18" t="n">
-        <v>62.6</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="19">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C19" t="n">
         <v>62.4</v>
@@ -1437,40 +1437,40 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C20" t="n">
-        <v>62.2</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C21" t="n">
-        <v>61.4</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C22" t="n">
-        <v>61.1</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="23">
@@ -1480,20 +1480,20 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C23" t="n">
-        <v>58.6</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LYC</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C24" t="n">
         <v>57.9</v>
@@ -1502,27 +1502,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>LYC</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C25" t="n">
-        <v>57.8</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C26" t="n">
-        <v>57.6</v>
+        <v>57.8</v>
       </c>
     </row>
   </sheetData>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-75.3</v>
+        <v>-75.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-70.8</v>
+        <v>-70.7</v>
       </c>
     </row>
     <row r="6">
@@ -1681,31 +1681,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XRO</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Xero</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-65.59999999999999</v>
+        <v>-65.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>XRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>Xero</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-65.2</v>
+        <v>-65.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1831,12 +1831,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EBO</t>
+          <t>LLC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EBOS Group</t>
+          <t>Lendlease</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1846,16 +1846,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LLC</t>
+          <t>EBO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lendlease</t>
+          <t>EBOS Group</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-56.6</v>
+        <v>-56</v>
       </c>
     </row>
     <row r="21">
@@ -1936,16 +1936,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TNE</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TechnologyOne</t>
+          <t>Champion Iron</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-50.6</v>
+        <v>-49.7</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.87</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.51</v>
+        <v>45.55</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.22</v>
+        <v>44.25</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.4</v>
+        <v>40.43</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.59</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.1</v>
+        <v>33.17</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.78</v>
+        <v>27.73</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.81</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.38</v>
+        <v>22.37</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.22</v>
+        <v>22.18</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>14.04</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>47.28</v>
+        <v>48.09</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>33.55</v>
+        <v>30.44</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>15.92</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>15.52</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>5.17</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>2.53</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.35</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.27</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>-4.98</v>
+        <v>-5.04</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-12.19</v>
+        <v>-13.18</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-21.43</v>
+        <v>-21.17</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>816.7</v>
+        <v>750</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>141.6</v>
+        <v>142.8</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>123.6</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>119.9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>104.3</v>
+        <v>102.6</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>102.2</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="8">
@@ -789,18 +789,18 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>94.59999999999999</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>83.5</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>83.09999999999999</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="12">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>81.7</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="13">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>81</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,18 +909,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>77.90000000000001</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>77</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>76.59999999999999</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -969,38 +969,38 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>72.7</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>70.40000000000001</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>70.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,58 +1029,58 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>69.2</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>67.3</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capricorn Metals</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>63.8</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Capricorn Metals</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>62.4</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61.9</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>61.9</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>60.8</v>
+        <v>62.9</v>
       </c>
     </row>
   </sheetData>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C2" t="n">
         <v>138.8</v>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>104.3</v>
+        <v>104.2</v>
       </c>
     </row>
     <row r="4">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C4" t="n">
         <v>100.4</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>79.90000000000001</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>78.7</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="8">
@@ -1285,49 +1285,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72.2</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>71.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>69.8</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>69.5</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>66.8</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="14">
@@ -1363,20 +1363,20 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>65.90000000000001</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C15" t="n">
         <v>64.59999999999999</v>
@@ -1385,50 +1385,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>63.4</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>63.1</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C19" t="n">
         <v>62.4</v>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>61.2</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>59.1</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>58.7</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="24">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>57.9</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="25">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.9</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="26">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.8</v>
+        <v>57.7</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.95</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.55</v>
+        <v>45.58</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.25</v>
+        <v>44.24</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.43</v>
+        <v>40.45</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.57</v>
+        <v>36.56</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.17</v>
+        <v>33.14</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.73</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.8</v>
+        <v>26.81</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.37</v>
+        <v>22.33</v>
       </c>
     </row>
     <row r="11">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14.04</v>
+        <v>14.03</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>48.09</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>30.44</v>
+        <v>34.03</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>19.32</v>
+        <v>19.93</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>5.29</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>1.52</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="8">
@@ -543,33 +543,33 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.13</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-3.96</v>
+        <v>-5.77</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-5.04</v>
+        <v>-7.11</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-13.18</v>
+        <v>-12.42</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-21.17</v>
+        <v>-23.41</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>750</v>
+        <v>815.6</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>142.8</v>
+        <v>148.3</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>125.4</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>122</v>
+        <v>123.8</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>102.6</v>
+        <v>113.1</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>101.5</v>
+        <v>100.7</v>
       </c>
     </row>
     <row r="8">
@@ -789,18 +789,18 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>95.59999999999999</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -809,38 +809,38 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>85.59999999999999</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>84.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>84.2</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,18 +869,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>83.2</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>82.2</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,18 +909,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>79.8</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,18 +929,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>77.90000000000001</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,58 +949,58 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>77.09999999999999</v>
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>74.59999999999999</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>74.3</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>AAI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Alcoa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,27 +1009,27 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>72.09999999999999</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>71.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1049,58 +1049,58 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>70.3</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>65.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capricorn Metals</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>65</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>63.6</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Capricorn Metals</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>63.5</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>62.9</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>138.8</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="3">
@@ -1236,85 +1236,85 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>100.4</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TUA</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>81.5</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>79.8</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>78.5</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>TUA</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>78.2</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>72.09999999999999</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1340,7 +1340,7 @@
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>69.3</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1418,7 +1418,7 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="19">
@@ -1431,33 +1431,33 @@
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>62.4</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.2</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>61.1</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="22">
@@ -1470,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>59</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="23">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-65.09999999999999</v>
+        <v>-64.3</v>
       </c>
     </row>
     <row r="11">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-56</v>
+        <v>-55.9</v>
       </c>
     </row>
     <row r="21">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.58</v>
+        <v>45.81</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.24</v>
+        <v>44.25</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.45</v>
+        <v>40.48</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.56</v>
+        <v>36.58</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.14</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.7</v>
+        <v>27.63</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.81</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="10">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.18</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14.03</v>
+        <v>14.11</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>49.92</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>34.03</v>
+        <v>26.65</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>19.93</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>15.8</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="6">
@@ -517,33 +517,33 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>4.33</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>0.78</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.63</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.77</v>
+        <v>-6.59</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-7.11</v>
+        <v>-8.119999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-12.42</v>
+        <v>-12.11</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-23.41</v>
+        <v>-24.95</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>815.6</v>
+        <v>698</v>
       </c>
     </row>
     <row r="3">
@@ -689,18 +689,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>148.3</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>126.6</v>
+        <v>127.1</v>
       </c>
     </row>
     <row r="5">
@@ -729,18 +729,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>123.8</v>
+        <v>123.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -749,18 +749,18 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>113.1</v>
+        <v>122.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -769,18 +769,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>100.7</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>97.90000000000001</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>95</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>89.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>87.40000000000001</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,18 +869,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>85.2</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>85.2</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,18 +909,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>84.7</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,18 +929,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>83.40000000000001</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>79.09999999999999</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="17">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>78.2</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,78 +989,78 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>77.59999999999999</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AAI</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alcoa</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>75.40000000000001</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>73.59999999999999</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>71.7</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Capricorn Metals</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,27 +1069,27 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>71.09999999999999</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>68.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1109,47 +1109,47 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>67.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capricorn Metals</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>66.09999999999999</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Paladin Energy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>65.59999999999999</v>
+        <v>63.7</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>138.6</v>
+        <v>138.5</v>
       </c>
     </row>
     <row r="3">
@@ -1249,7 +1249,7 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>79.5</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1307,27 +1307,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>71.90000000000001</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>71.8</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1340,7 +1340,7 @@
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>69.40000000000001</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="13">
@@ -1366,7 +1366,7 @@
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>65.8</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>64.59999999999999</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>60.5</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="22">
@@ -1470,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>59.1</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="23">
@@ -1509,20 +1509,20 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.8</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
     </row>
   </sheetData>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-64.3</v>
+        <v>-64.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.92</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.81</v>
+        <v>45.76</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.25</v>
+        <v>44.27</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.48</v>
+        <v>40.45</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.58</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.07</v>
+        <v>33.06</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.63</v>
+        <v>27.58</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.88</v>
+        <v>26.93</v>
       </c>
     </row>
     <row r="10">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.2</v>
+        <v>22.16</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14.11</v>
+        <v>14.16</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,33 +465,33 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>47.62</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>26.65</v>
+        <v>19.53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>20.5</v>
+        <v>18.13</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>14.8</v>
+        <v>14.03</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>4.88</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>3.84</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.28</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-6.59</v>
+        <v>-7.81</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-8.119999999999999</v>
+        <v>-8.24</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-12.11</v>
+        <v>-11.22</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-24.95</v>
+        <v>-24.07</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>698</v>
+        <v>586.8</v>
       </c>
     </row>
     <row r="3">
@@ -689,47 +689,47 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>148</v>
+        <v>137.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>127.1</v>
+        <v>126.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>123.3</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="6">
@@ -749,18 +749,18 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>122.4</v>
+        <v>116.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -769,18 +769,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>97.5</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,58 +789,58 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>95.7</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>92.09999999999999</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>85.59999999999999</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>85</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>83.2</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="13">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>82</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="14">
@@ -909,18 +909,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>80.2</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,38 +929,38 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>76.8</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>76.3</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>75.7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18">
@@ -989,38 +989,38 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>75.7</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>73.2</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,58 +1029,58 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>69.5</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>68.09999999999999</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capricorn Metals</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>67.5</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Capricorn Metals</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,67 +1089,67 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>65.90000000000001</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>65.59999999999999</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>64</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Paladin Energy</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>63.7</v>
+        <v>59.4</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>138.5</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>99.8</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="5">
@@ -1249,7 +1249,7 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>79.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1262,7 +1262,7 @@
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>75.90000000000001</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
@@ -1301,7 +1301,7 @@
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="10">
@@ -1340,7 +1340,7 @@
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>69.3</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="13">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>66.7</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1366,7 +1366,7 @@
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>65.90000000000001</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="15">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>64.90000000000001</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="16">
@@ -1405,7 +1405,7 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>63.3</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="18">
@@ -1418,7 +1418,7 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.9</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>60.4</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="22">
@@ -1496,7 +1496,7 @@
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>57.8</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="25">
@@ -1509,20 +1509,20 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.7</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.6</v>
+        <v>57.7</v>
       </c>
     </row>
   </sheetData>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-70.7</v>
+        <v>-70.3</v>
       </c>
     </row>
     <row r="6">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.95</v>
+        <v>48.99</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.76</v>
+        <v>45.74</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.27</v>
+        <v>44.24</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.45</v>
+        <v>40.43</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.57</v>
+        <v>36.55</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.06</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.58</v>
+        <v>27.52</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.93</v>
+        <v>26.96</v>
       </c>
     </row>
     <row r="10">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.16</v>
+        <v>22.15</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14.16</v>
+        <v>14.11</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>45.2</v>
+        <v>46.33</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>19.53</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>18.13</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="5">
@@ -504,33 +504,33 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>14.03</v>
+        <v>12.77</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>3.19</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.33</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.81</v>
+        <v>-10.62</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-8.24</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-11.22</v>
+        <v>-11.14</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-24.07</v>
+        <v>-25.15</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>586.8</v>
+        <v>545.2</v>
       </c>
     </row>
     <row r="3">
@@ -689,27 +689,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>137.2</v>
+        <v>132.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>126.5</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5">
@@ -729,27 +729,27 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>125.5</v>
+        <v>124.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>116.9</v>
+        <v>115.2</v>
       </c>
     </row>
     <row r="7">
@@ -769,18 +769,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>92.59999999999999</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,58 +789,58 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>89.2</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>86.8</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>83.8</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>83.3</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,18 +869,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>82.2</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>81.5</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,58 +909,58 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>78.3</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>75.8</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>73.5</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>71</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,27 +989,27 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>70.7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>70.09999999999999</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="20">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>68.7</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,38 +1049,38 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>67.40000000000001</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Capricorn Metals</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>64.2</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capricorn Metals</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,38 +1089,38 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>63.8</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61.5</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>60.7</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>Paladin Energy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>59.4</v>
+        <v>59.8</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C2" t="n">
-        <v>138.6</v>
+        <v>138.7</v>
       </c>
     </row>
     <row r="3">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C3" t="n">
         <v>104.2</v>
@@ -1233,36 +1233,36 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C4" t="n">
-        <v>99.5</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C5" t="n">
-        <v>78.90000000000001</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C7" t="n">
-        <v>78.2</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C8" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C9" t="n">
-        <v>72.2</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C10" t="n">
-        <v>71.7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C11" t="n">
-        <v>71.59999999999999</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C12" t="n">
-        <v>69.2</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C13" t="n">
-        <v>66.90000000000001</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C14" t="n">
-        <v>65.8</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C15" t="n">
-        <v>65.2</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C16" t="n">
-        <v>64.5</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="17">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C17" t="n">
-        <v>63.6</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="18">
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C18" t="n">
         <v>63</v>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C19" t="n">
-        <v>62.2</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C20" t="n">
-        <v>61.1</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C21" t="n">
-        <v>60.5</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="22">
@@ -1467,62 +1467,62 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C22" t="n">
-        <v>58.7</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C23" t="n">
-        <v>58.6</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C24" t="n">
-        <v>57.9</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LYC</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C25" t="n">
-        <v>57.8</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C26" t="n">
-        <v>57.7</v>
+        <v>57.9</v>
       </c>
     </row>
   </sheetData>
@@ -1621,31 +1621,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COH</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cochlear</t>
+          <t>Zip</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-70.3</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>COH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zip</t>
+          <t>Cochlear</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-70</v>
+        <v>-69.8</v>
       </c>
     </row>
     <row r="7">
@@ -1846,12 +1846,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EBO</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EBOS Group</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1861,16 +1861,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>EBO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>EBOS Group</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-55.9</v>
+        <v>-55.8</v>
       </c>
     </row>
     <row r="22">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.99</v>
+        <v>49.04</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.74</v>
+        <v>45.67</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.24</v>
+        <v>44.12</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.43</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.55</v>
+        <v>36.53</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.07</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.52</v>
+        <v>27.57</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.96</v>
+        <v>26.85</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.33</v>
+        <v>22.34</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.15</v>
+        <v>22.18</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14.11</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>46.33</v>
+        <v>43.91</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>20.33</v>
+        <v>22.13</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>15.57</v>
+        <v>17.41</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>12.77</v>
+        <v>12.45</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>4.05</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>3.01</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="8">
@@ -543,33 +543,33 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.4</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>-10.62</v>
+        <v>-11.43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>-10.67</v>
+        <v>-11.71</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-11.14</v>
+        <v>-12.73</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.15</v>
+        <v>-25.88</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>545.2</v>
+        <v>553.9</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>132.5</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>125</v>
+        <v>119.9</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>124.2</v>
+        <v>117.2</v>
       </c>
     </row>
     <row r="6">
@@ -749,18 +749,18 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>115.2</v>
+        <v>110.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -769,18 +769,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>93.7</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>93.2</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9">
@@ -815,52 +815,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>86.8</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>85.40000000000001</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,78 +869,78 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>81</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>80.59999999999999</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>77.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>76.2</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,18 +949,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>75.3</v>
+        <v>74.09999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>74.3</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,27 +989,27 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>74</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>73.2</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>72.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>71.5</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="22">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>70.5</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,38 +1089,38 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>68.8</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Paladin Energy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>64.5</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>62.3</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Paladin Energy</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>59.8</v>
+        <v>59.7</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>138.7</v>
+        <v>138.4</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>104.2</v>
+        <v>104.1</v>
       </c>
     </row>
     <row r="4">
@@ -1233,36 +1233,36 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="8">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
         <v>76.09999999999999</v>
@@ -1298,36 +1298,36 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72.40000000000001</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>72</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>69.5</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>67.09999999999999</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>65.90000000000001</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>65.3</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="16">
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C16" t="n">
         <v>64.7</v>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C17" t="n">
         <v>63.7</v>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="19">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>62.3</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>60.1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C22" t="n">
         <v>58.9</v>
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>58.7</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="24">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>58.7</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="25">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" t="n">
         <v>58</v>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.9</v>
+        <v>57.8</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.04</v>
+        <v>49.01</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.67</v>
+        <v>45.63</v>
       </c>
     </row>
     <row r="4">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.46</v>
+        <v>40.42</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.53</v>
+        <v>36.67</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.1</v>
+        <v>33.12</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.57</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.85</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.34</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.18</v>
+        <v>22.17</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>14.03</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>43.91</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>22.13</v>
+        <v>21.96</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>17.41</v>
+        <v>20.79</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>12.45</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>4.53</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="8">
@@ -543,33 +543,33 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.75</v>
+        <v>-3.31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-11.43</v>
+        <v>-11.68</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-11.71</v>
+        <v>-12.98</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-12.73</v>
+        <v>-14.57</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.88</v>
+        <v>-25.79</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>553.9</v>
+        <v>576.8</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>131.2</v>
+        <v>122.5</v>
       </c>
     </row>
     <row r="4">
@@ -709,47 +709,47 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>119.9</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>117.2</v>
+        <v>111.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>110.7</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>93.2</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -789,18 +789,18 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>93</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -809,118 +809,118 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>87.2</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>83.40000000000001</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>81</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>77.5</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>76.8</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>74.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,18 +929,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>74.3</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="17">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>73</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>70.8</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>70.09999999999999</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="20">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>69.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>67.7</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capricorn Metals</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>65.8</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Capricorn Metals</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,38 +1089,38 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>63.1</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Paladin Energy</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>62.7</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>60.4</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>59.7</v>
+        <v>59.6</v>
       </c>
     </row>
   </sheetData>
@@ -1249,13 +1249,13 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>78.90000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1268,7 +1268,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1294,27 +1294,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72.2</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="11">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1405,7 +1405,7 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>63.7</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="18">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="22">
@@ -1470,13 +1470,13 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>58.9</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1489,14 +1489,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>58.6</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="25">
@@ -1681,76 +1681,76 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>XRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>Xero</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-65.2</v>
+        <v>-64.09999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XRO</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Xero</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-64.09999999999999</v>
+        <v>-63.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>Austal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-63.4</v>
+        <v>-61.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Austal</t>
+          <t>Seek</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-61.3</v>
+        <v>-58.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Seek</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-58.7</v>
+        <v>-58.2</v>
       </c>
     </row>
     <row r="14">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.01</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.63</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.12</v>
+        <v>44.14</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.42</v>
+        <v>40.47</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.67</v>
+        <v>36.82</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.12</v>
+        <v>33.08</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.59</v>
+        <v>27.61</v>
       </c>
     </row>
     <row r="9">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.38</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.17</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14.03</v>
+        <v>14.02</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,33 +465,33 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>43.92</v>
+        <v>54.52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>21.96</v>
+        <v>27.97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>20.79</v>
+        <v>25.08</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>13.5</v>
+        <v>14.61</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>4.23</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>2.66</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="8">
@@ -543,46 +543,46 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.31</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-11.68</v>
+        <v>-9.52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>-12.98</v>
+        <v>-12.69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-14.57</v>
+        <v>-13.09</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.79</v>
+        <v>-25.78</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +625,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>576.8</v>
+        <v>673.1</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>122.5</v>
+        <v>142.4</v>
       </c>
     </row>
     <row r="4">
@@ -709,58 +709,58 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>111.9</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>108.8</v>
+        <v>123.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -769,18 +769,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>88.90000000000001</v>
+        <v>120.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,58 +789,58 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>85.3</v>
+        <v>109.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>84.09999999999999</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>82</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,58 +849,58 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>81.3</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>80.8</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>78.3</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,18 +909,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>77.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,38 +929,38 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>75.8</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>74.7</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>72.3</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,38 +989,38 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>71.5</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>71.3</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>66.90000000000001</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Capricorn Metals</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>66.90000000000001</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,27 +1069,27 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>66</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capricorn Metals</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>65.5</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>59.6</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>59.6</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>138.4</v>
+        <v>138.2</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>104.1</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="4">
@@ -1236,46 +1236,46 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>99.7</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>79</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>78.59999999999999</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>78.5</v>
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1340,7 +1340,7 @@
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>69.3</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="13">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>67.09999999999999</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14">
@@ -1366,33 +1366,33 @@
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>65.8</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>65.2</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>64.7</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1405,7 +1405,7 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>64.2</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1418,7 +1418,7 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.9</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="19">
@@ -1431,7 +1431,7 @@
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>62.2</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="20">
@@ -1444,7 +1444,7 @@
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.2</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="21">
@@ -1457,72 +1457,72 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>59.9</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>59</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>58.6</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>58</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.8</v>
+        <v>58.4</v>
       </c>
     </row>
   </sheetData>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-64.09999999999999</v>
+        <v>-63.8</v>
       </c>
     </row>
     <row r="10">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.06</v>
+        <v>49.16</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.75</v>
+        <v>45.84</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.14</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.47</v>
+        <v>40.45</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.82</v>
+        <v>36.74</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.08</v>
+        <v>33.11</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.61</v>
+        <v>27.62</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.92</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.46</v>
+        <v>22.51</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.2</v>
+        <v>22.27</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14.02</v>
+        <v>13.94</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,33 +465,33 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>54.52</v>
+        <v>53.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>27.97</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>25.08</v>
+        <v>20.92</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>14.61</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>3.56</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>2.04</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.47</v>
+        <v>-5.97</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-9.52</v>
+        <v>-13.59</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>-12.69</v>
+        <v>-13.85</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-13.09</v>
+        <v>-16.22</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.78</v>
+        <v>-25.26</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>673.1</v>
+        <v>590.1</v>
       </c>
     </row>
     <row r="3">
@@ -689,27 +689,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>142.4</v>
+        <v>146.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5">
@@ -729,27 +729,27 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>130</v>
+        <v>129.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>123.1</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>120.1</v>
+        <v>124.3</v>
       </c>
     </row>
     <row r="8">
@@ -789,38 +789,38 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>109.1</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>108.8</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>98.7</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>96.90000000000001</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,18 +869,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>94.5</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>93.8</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,27 +909,27 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>91.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>89.5</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -949,38 +949,38 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>87.09999999999999</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>85.7</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,38 +989,38 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>83.3</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>82.5</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>82.5</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="21">
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>82.3</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="22">
@@ -1069,38 +1069,38 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>78.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>77.2</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>75.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>69.40000000000001</v>
+        <v>69.2</v>
       </c>
     </row>
   </sheetData>
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>103.5</v>
+        <v>103.7</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>98.90000000000001</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="5">
@@ -1249,7 +1249,7 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>80.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>76.09999999999999</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1327,7 +1327,7 @@
         <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>71.90000000000001</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
@@ -1340,7 +1340,7 @@
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>69.7</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="13">
@@ -1470,13 +1470,13 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>58.7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1489,40 +1489,40 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>58.6</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>58.6</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>58.4</v>
+        <v>58.2</v>
       </c>
     </row>
   </sheetData>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-63.8</v>
+        <v>-63.6</v>
       </c>
     </row>
     <row r="10">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.16</v>
+        <v>49.21</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.84</v>
+        <v>45.88</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.2</v>
+        <v>44.18</v>
       </c>
     </row>
     <row r="5">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.74</v>
+        <v>36.56</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.11</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="8">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.94</v>
+        <v>26.91</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.51</v>
+        <v>22.52</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.27</v>
+        <v>22.28</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.94</v>
+        <v>13.91</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>53.64</v>
+        <v>54.05</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>23.75</v>
+        <v>24.58</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>20.92</v>
+        <v>20.64</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>12.1</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>4.18</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>1.33</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="8">
@@ -543,46 +543,46 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.97</v>
+        <v>-5.83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-13.59</v>
+        <v>-14.57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-13.85</v>
+        <v>-15.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-16.22</v>
+        <v>-16.35</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.26</v>
+        <v>-23.44</v>
       </c>
     </row>
   </sheetData>
@@ -626,7 +626,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -669,18 +669,18 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>590.1</v>
+        <v>579.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -689,38 +689,38 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>146.2</v>
+        <v>153.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>135</v>
+        <v>144.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,38 +729,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>129.4</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>125</v>
+        <v>118.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -769,18 +769,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>124.3</v>
+        <v>118.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>97.8</v>
+        <v>101.6</v>
       </c>
     </row>
     <row r="9">
@@ -809,18 +809,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>96.3</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>95.8</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="11">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>95.59999999999999</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,18 +869,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>94.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>94.09999999999999</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,78 +909,78 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>92.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>89.40000000000001</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>89.3</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>89.2</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>88.59999999999999</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>84.8</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>79.8</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="21">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>79.3</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,38 +1069,38 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>77.90000000000001</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>73.7</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,38 +1109,38 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>72.7</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Paladin Energy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>70.09999999999999</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>69.2</v>
+        <v>67.2</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C2" t="n">
-        <v>138.2</v>
+        <v>138.5</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C3" t="n">
-        <v>103.7</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="4">
@@ -1233,46 +1233,46 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C4" t="n">
-        <v>98.7</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C5" t="n">
-        <v>81.90000000000001</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
-        <v>79.5</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C7" t="n">
         <v>79.2</v>
@@ -1285,36 +1285,36 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C8" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C9" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C10" t="n">
-        <v>72.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C11" t="n">
         <v>72</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C12" t="n">
-        <v>69.8</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1363,33 +1363,33 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C14" t="n">
-        <v>65.7</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C15" t="n">
-        <v>65.40000000000001</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C16" t="n">
         <v>65.09999999999999</v>
@@ -1398,14 +1398,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C17" t="n">
-        <v>64.90000000000001</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C18" t="n">
-        <v>63.4</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="19">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C19" t="n">
-        <v>62.7</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C20" t="n">
-        <v>61.6</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C21" t="n">
-        <v>60.8</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="22">
@@ -1467,23 +1467,23 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C22" t="n">
-        <v>59</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C23" t="n">
-        <v>58.7</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="24">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C24" t="n">
         <v>58.7</v>
@@ -1502,27 +1502,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C25" t="n">
-        <v>58.4</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C26" t="n">
-        <v>58.2</v>
+        <v>57.6</v>
       </c>
     </row>
   </sheetData>
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-69.8</v>
+        <v>-69.7</v>
       </c>
     </row>
     <row r="7">
@@ -1681,31 +1681,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XRO</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Xero</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-63.6</v>
+        <v>-63.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>XRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>Xero</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-63.4</v>
+        <v>-62.9</v>
       </c>
     </row>
     <row r="11">
@@ -1741,12 +1741,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>Deep Yellow</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1756,42 +1756,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deep Yellow</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-58.2</v>
+        <v>-57.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TWE</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Treasury Wine Estates</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-57.6</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1801,27 +1801,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>ARB Corporation</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-57.5</v>
+        <v>-57.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>TWE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ARB Corporation</t>
+          <t>Treasury Wine Estates</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1861,46 +1861,46 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EBO</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EBOS Group</t>
+          <t>Telix Pharmaceuticals</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-55.8</v>
+        <v>-54.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Telix Pharmaceuticals</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-54.4</v>
+        <v>-54.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>EBO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>EBOS Group</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-54.3</v>
+        <v>-54</v>
       </c>
     </row>
     <row r="24">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.21</v>
+        <v>49.24</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.88</v>
+        <v>45.82</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.18</v>
+        <v>44.01</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.45</v>
+        <v>40.42</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.56</v>
+        <v>36.37</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.1</v>
+        <v>33.02</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.62</v>
+        <v>27.45</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.91</v>
+        <v>26.83</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.52</v>
+        <v>22.47</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.28</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.91</v>
+        <v>13.87</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>54.05</v>
+        <v>53.22</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>24.58</v>
+        <v>25.14</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>20.64</v>
+        <v>23.29</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>12.62</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>4.02</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>0.31</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="8">
@@ -543,33 +543,33 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.83</v>
+        <v>-4.65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>-14.57</v>
+        <v>-14.09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>-15.57</v>
+        <v>-14.56</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-16.35</v>
+        <v>-14.8</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-23.44</v>
+        <v>-22.99</v>
       </c>
     </row>
   </sheetData>
@@ -626,7 +626,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -669,18 +669,18 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>579.6</v>
+        <v>618.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -689,18 +689,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>153.2</v>
+        <v>145.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,18 +709,18 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>144.7</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,78 +729,78 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>129.5</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>118.9</v>
+        <v>117.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>118.4</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>101.6</v>
+        <v>109.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>98.8</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>98.5</v>
+        <v>102.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>102.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>94.59999999999999</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="13">
@@ -895,52 +895,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>92.40000000000001</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>91.5</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>88.90000000000001</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="17">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>87.8</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>86.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>77.8</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>77.5</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capricorn Metals</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>77</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Capricorn Metals</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,67 +1069,67 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>70.7</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Paladin Energy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>70.59999999999999</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Paladin Energy</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>68.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>67.2</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>138.5</v>
+        <v>138.3</v>
       </c>
     </row>
     <row r="3">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C3" t="n">
         <v>103.8</v>
@@ -1233,36 +1233,36 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>98.90000000000001</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>79.5</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>79.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72.90000000000001</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>72.40000000000001</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>72</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>69.90000000000001</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>67.59999999999999</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="14">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" t="n">
         <v>65.8</v>
@@ -1372,24 +1372,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>65.2</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C16" t="n">
         <v>65.09999999999999</v>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>65.09999999999999</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>63.5</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="19">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>62.3</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.7</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="21">
@@ -1454,36 +1454,36 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>60.5</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>59.1</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>58.8</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="24">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>58.7</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="25">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" t="n">
         <v>58.2</v>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.6</v>
+        <v>57.4</v>
       </c>
     </row>
   </sheetData>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.82</v>
+        <v>45.83</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.01</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.42</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.37</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.02</v>
+        <v>33.06</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.45</v>
+        <v>27.43</v>
       </c>
     </row>
     <row r="9">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.2</v>
+        <v>22.23</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.87</v>
+        <v>13.88</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>53.22</v>
+        <v>55.28</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>25.14</v>
+        <v>23.41</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>23.29</v>
+        <v>21.83</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>13.32</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>4.52</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.65</v>
+        <v>-5.81</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>-14.09</v>
+        <v>-13.29</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>-14.56</v>
+        <v>-14.57</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-14.8</v>
+        <v>-17.09</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-22.99</v>
+        <v>-22.3</v>
       </c>
     </row>
   </sheetData>
@@ -626,7 +626,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -669,18 +669,18 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>618.5</v>
+        <v>599.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -689,18 +689,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>145.2</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,18 +709,18 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,98 +729,98 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>119</v>
+        <v>123.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>117.1</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>110.5</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>109.9</v>
+        <v>109.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>104</v>
+        <v>108.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>102.9</v>
+        <v>105.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>102.9</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,58 +869,58 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>96.7</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>94.59999999999999</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>94.40000000000001</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,18 +929,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>94.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,18 +949,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>94.2</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>91.40000000000001</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>90.59999999999999</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>80.2</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>80.2</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>79.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capricorn Metals</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,47 +1069,47 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>77.2</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Paladin Energy</t>
+          <t>Capricorn Metals</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>71.8</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>70.5</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>70.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Paladin Energy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>69.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>103.8</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>101.2</v>
+        <v>101.1</v>
       </c>
     </row>
     <row r="5">
@@ -1249,33 +1249,33 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>79.59999999999999</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>75.90000000000001</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
@@ -1301,7 +1301,7 @@
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>73</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="10">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>72.2</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="11">
@@ -1327,7 +1327,7 @@
         <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>71.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C12" t="n">
-        <v>69.7</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>67.5</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>65.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1418,7 +1418,7 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>63.4</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="19">
@@ -1431,7 +1431,7 @@
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>62.2</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="20">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>60.4</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="22">
@@ -1470,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>59</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="23">
@@ -1522,7 +1522,7 @@
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.4</v>
+        <v>57.3</v>
       </c>
     </row>
   </sheetData>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-62.9</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="11">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-54</v>
+        <v>-53.5</v>
       </c>
     </row>
     <row r="24">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.24</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.83</v>
+        <v>45.88</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>43.93</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.46</v>
+        <v>40.58</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.36</v>
+        <v>36.32</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.06</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="8">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.47</v>
+        <v>22.48</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.23</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.88</v>
+        <v>13.87</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,33 +465,33 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>55.28</v>
+        <v>48.86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>23.41</v>
+        <v>24.18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>21.83</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>13.83</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>6.48</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>1.89</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="8">
@@ -543,33 +543,33 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.81</v>
+        <v>-4.93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-13.29</v>
+        <v>-15.35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-14.57</v>
+        <v>-16.67</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-17.09</v>
+        <v>-17.44</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-22.3</v>
+        <v>-22.96</v>
       </c>
     </row>
   </sheetData>
@@ -626,7 +626,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -669,18 +669,18 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>599.1</v>
+        <v>613.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -689,18 +689,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>146</v>
+        <v>133.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>146</v>
+        <v>120.1</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>123.8</v>
+        <v>106.8</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>110.2</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>109.7</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -789,38 +789,38 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>109.3</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>108.1</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>105.2</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>104.4</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,38 +869,38 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>100.5</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>98.8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,18 +909,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>95.90000000000001</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,18 +929,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>95.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,18 +949,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>92.7</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>91.7</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,38 +989,38 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>91</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>90.7</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>90.40000000000001</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>84.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>82.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capricorn Metals</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>75.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>72.40000000000001</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>Capricorn Metals</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>71.59999999999999</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Paladin Energy</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>69.59999999999999</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>104.4</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4">
@@ -1236,33 +1236,33 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>101.1</v>
+        <v>100.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>79.59999999999999</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79.2</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="8">
@@ -1301,7 +1301,7 @@
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72.7</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C12" t="n">
         <v>69.90000000000001</v>
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>67.40000000000001</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="14">
@@ -1366,46 +1366,46 @@
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>65.8</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>65.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>65.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>65</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="18">
@@ -1418,7 +1418,7 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>63.3</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="19">
@@ -1431,7 +1431,7 @@
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.7</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="20">
@@ -1457,33 +1457,33 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>60.6</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>59.1</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>58.9</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="24">
@@ -1496,7 +1496,7 @@
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>58.6</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="25">
@@ -1591,31 +1591,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>DRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wisetech Global</t>
+          <t>Droneshield</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-75.09999999999999</v>
+        <v>-74.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DRO</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Droneshield</t>
+          <t>Wisetech Global</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-74.3</v>
+        <v>-71.7</v>
       </c>
     </row>
     <row r="5">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-62.5</v>
+        <v>-62.4</v>
       </c>
     </row>
     <row r="11">
@@ -1801,12 +1801,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>TWE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ARB Corporation</t>
+          <t>Treasury Wine Estates</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1816,136 +1816,136 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TWE</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Treasury Wine Estates</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-57.3</v>
+        <v>-57.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LLC</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lendlease</t>
+          <t>ARB Corporation</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-56.6</v>
+        <v>-56.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>LLC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>Lendlease</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-55.9</v>
+        <v>-56.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Telix Pharmaceuticals</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-54.4</v>
+        <v>-54.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>Telix Pharmaceuticals</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-54.3</v>
+        <v>-53.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EBO</t>
+          <t>LOV</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EBOS Group</t>
+          <t>Lovisa</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-53.5</v>
+        <v>-51.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LOV</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lovisa</t>
+          <t>Catalyst Metals</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-51.5</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Catalyst Metals</t>
+          <t>Champion Iron</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-51</v>
+        <v>-49.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>TNE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Champion Iron</t>
+          <t>TechnologyOne</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-49.7</v>
+        <v>-49.3</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.29</v>
+        <v>49.26</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.88</v>
+        <v>45.69</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43.93</v>
+        <v>43.85</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.58</v>
+        <v>40.53</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.32</v>
+        <v>36.27</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.1</v>
+        <v>32.95</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.43</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.83</v>
+        <v>26.79</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.48</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.25</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.87</v>
+        <v>13.83</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>48.86</v>
+        <v>52.35</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>24.18</v>
+        <v>30.38</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>20.59</v>
+        <v>22.27</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>10.68</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>6.13</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.1</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="8">
@@ -543,46 +543,46 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.93</v>
+        <v>-5.59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-15.35</v>
+        <v>-15.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>-16.67</v>
+        <v>-16.63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-17.44</v>
+        <v>-18.58</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-22.96</v>
+        <v>-22.82</v>
       </c>
     </row>
   </sheetData>
@@ -626,7 +626,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -669,18 +669,18 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>613.7</v>
+        <v>658.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -689,18 +689,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>133.6</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>120.1</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>106.8</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>104.8</v>
+        <v>105.3</v>
       </c>
     </row>
     <row r="7">
@@ -769,18 +769,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>99.59999999999999</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,38 +789,38 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>96.2</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>90.7</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>89</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>87.5</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,18 +869,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>85.3</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>84</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,38 +909,38 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>83.5</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>83.09999999999999</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,18 +949,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>82.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>81.5</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,58 +989,58 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>81.40000000000001</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>79.90000000000001</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>79.8</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>79.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>74.59999999999999</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="23">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>70.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>66.09999999999999</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capricorn Metals</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>65</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Capricorn Metals</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>64.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>138.3</v>
+        <v>138.1</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>100.4</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="5">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1340,7 +1340,7 @@
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>69.90000000000001</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="13">
@@ -1366,26 +1366,26 @@
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>67.5</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>65.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1431,7 +1431,7 @@
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.6</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="20">
@@ -1444,7 +1444,7 @@
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="21">
@@ -1470,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>59</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="23">
@@ -1483,7 +1483,7 @@
         <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="24">
@@ -1522,7 +1522,7 @@
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.3</v>
+        <v>57.4</v>
       </c>
     </row>
   </sheetData>
@@ -1726,106 +1726,106 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Seek</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-58.7</v>
+        <v>-60.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deep Yellow</t>
+          <t>Seek</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-58.2</v>
+        <v>-58.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>Deep Yellow</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-57.7</v>
+        <v>-58.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-57.5</v>
+        <v>-57.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-57.5</v>
+        <v>-57.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TWE</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Treasury Wine Estates</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-57.3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>TWE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>Treasury Wine Estates</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-57.1</v>
+        <v>-57.3</v>
       </c>
     </row>
     <row r="19">
@@ -1876,76 +1876,76 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>LOV</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Telix Pharmaceuticals</t>
+          <t>Lovisa</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-53.1</v>
+        <v>-51.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LOV</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lovisa</t>
+          <t>Catalyst Metals</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-51.5</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Catalyst Metals</t>
+          <t>Champion Iron</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-51</v>
+        <v>-49.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>PMV</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Champion Iron</t>
+          <t>Premier Investments</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-49.7</v>
+        <v>-49.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TNE</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TechnologyOne</t>
+          <t>Telix Pharmaceuticals</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-49.3</v>
+        <v>-49.1</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.26</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.69</v>
+        <v>45.66</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43.85</v>
+        <v>43.86</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.53</v>
+        <v>40.48</v>
       </c>
     </row>
     <row r="6">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.95</v>
+        <v>32.66</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.4</v>
+        <v>27.42</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.79</v>
+        <v>26.82</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.46</v>
+        <v>22.44</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.9</v>
+        <v>21.91</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.83</v>
+        <v>13.81</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,33 +465,33 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>52.35</v>
+        <v>47.87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>30.38</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>22.27</v>
+        <v>13.27</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>10.14</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>5.16</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.29</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="8">
@@ -543,33 +543,33 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.59</v>
+        <v>-6.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-15.72</v>
+        <v>-16.14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-16.63</v>
+        <v>-17.29</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-18.58</v>
+        <v>-19.52</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-22.82</v>
+        <v>-22.53</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>658.3</v>
+        <v>369.7</v>
       </c>
     </row>
     <row r="3">
@@ -689,38 +689,38 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>133</v>
+        <v>120.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>132.3</v>
+        <v>109.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,38 +729,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>119.1</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>105.3</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -769,18 +769,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>104</v>
+        <v>97.59999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,38 +789,38 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>99.8</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>98.7</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>96.90000000000001</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>90.8</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,18 +869,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>90.40000000000001</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>89.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,38 +909,38 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>89.09999999999999</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>88.5</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,18 +949,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>86.40000000000001</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>86.3</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>84.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>83.3</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="20">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>83.09999999999999</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>77.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>77.5</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>71.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1109,38 +1109,38 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>68.2</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>66.5</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capricorn Metals</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>64.90000000000001</v>
+        <v>64.2</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C2" t="n">
-        <v>138.1</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C3" t="n">
-        <v>104</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C4" t="n">
-        <v>100.2</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C5" t="n">
-        <v>79.3</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="6">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C6" t="n">
         <v>79.2</v>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C7" t="n">
         <v>78.8</v>
@@ -1285,20 +1285,20 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C8" t="n">
-        <v>76.09999999999999</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C9" t="n">
         <v>72.59999999999999</v>
@@ -1307,14 +1307,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C10" t="n">
-        <v>72.40000000000001</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C11" t="n">
-        <v>71.59999999999999</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C12" t="n">
-        <v>69.7</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C13" t="n">
-        <v>67.5</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="14">
@@ -1363,20 +1363,20 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C14" t="n">
-        <v>67.09999999999999</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C15" t="n">
         <v>64.90000000000001</v>
@@ -1385,27 +1385,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C16" t="n">
-        <v>64.90000000000001</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C17" t="n">
-        <v>64.7</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="18">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C18" t="n">
-        <v>63.5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C19" t="n">
-        <v>61.7</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C20" t="n">
-        <v>61.3</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="21">
@@ -1454,62 +1454,62 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C21" t="n">
-        <v>60.2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C22" t="n">
-        <v>58.9</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C23" t="n">
-        <v>58.6</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C24" t="n">
-        <v>58.5</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C25" t="n">
-        <v>58.2</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="26">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C26" t="n">
-        <v>57.4</v>
+        <v>57.3</v>
       </c>
     </row>
   </sheetData>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-71.7</v>
+        <v>-71</v>
       </c>
     </row>
     <row r="5">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-60.5</v>
+        <v>-60.3</v>
       </c>
     </row>
     <row r="13">
@@ -1831,31 +1831,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>LLC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ARB Corporation</t>
+          <t>Lendlease</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-56.9</v>
+        <v>-56.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LLC</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lendlease</t>
+          <t>ARB Corporation</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-56.6</v>
+        <v>-56.4</v>
       </c>
     </row>
     <row r="21">
@@ -1876,31 +1876,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LOV</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lovisa</t>
+          <t>Catalyst Metals</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-51.5</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>LOV</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Catalyst Metals</t>
+          <t>Lovisa</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-51</v>
+        <v>-50.4</v>
       </c>
     </row>
     <row r="24">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.29</v>
+        <v>49.35</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.66</v>
+        <v>45.46</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43.86</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.48</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.27</v>
+        <v>35.95</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.66</v>
+        <v>32.41</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.42</v>
+        <v>27.37</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.82</v>
+        <v>26.85</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.44</v>
+        <v>22.42</v>
       </c>
     </row>
     <row r="11">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.81</v>
+        <v>13.8</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>47.87</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>17.7</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>13.27</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>10.01</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>2.79</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-6.44</v>
+        <v>-6.13</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-16.14</v>
+        <v>-15.35</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-17.29</v>
+        <v>-18.06</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-19.52</v>
+        <v>-20.66</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-22.53</v>
+        <v>-23.48</v>
       </c>
     </row>
   </sheetData>
@@ -626,7 +626,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>369.7</v>
+        <v>341.3</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>120.6</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="4">
@@ -709,18 +709,18 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>109.1</v>
+        <v>113.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,18 +729,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>108.6</v>
+        <v>110.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -749,18 +749,18 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>108</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -769,58 +769,58 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>97.59999999999999</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>89.7</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>88.5</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>86.5</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>86.2</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,18 +869,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>86</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>85.59999999999999</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,18 +909,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,18 +929,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>77.59999999999999</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,18 +949,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>76.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>76.7</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>75.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>73.8</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="20">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>73</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>71.09999999999999</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="22">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>70.90000000000001</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>70.40000000000001</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>67.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>64.5</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>64.2</v>
+        <v>63.5</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>133</v>
+        <v>132.6</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>104.4</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>100.5</v>
+        <v>100.1</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>79.5</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="6">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
         <v>79.2</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>78.8</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1285,36 +1285,36 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>76.40000000000001</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="11">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C11" t="n">
         <v>71.3</v>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C12" t="n">
         <v>69.90000000000001</v>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>67.2</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>66.8</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>64.90000000000001</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>64.2</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C17" t="n">
         <v>63.3</v>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="19">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.5</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.5</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>60</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>58.5</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="23">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>58.4</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="24">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C24" t="n">
         <v>57.8</v>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.6</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="26">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
     </row>
   </sheetData>
@@ -1741,46 +1741,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Seek</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-58.7</v>
+        <v>-59.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deep Yellow</t>
+          <t>Seek</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-58.2</v>
+        <v>-58.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>Deep Yellow</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-57.8</v>
+        <v>-58.2</v>
       </c>
     </row>
     <row r="16">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.35</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.46</v>
+        <v>45.53</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43.87</v>
+        <v>43.98</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.54</v>
+        <v>40.57</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.95</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.41</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.37</v>
+        <v>27.53</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.85</v>
+        <v>27.36</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.42</v>
+        <v>22.83</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.91</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.8</v>
+        <v>13.86</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>46.83</v>
+        <v>42.57</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>19.17</v>
+        <v>17.38</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>10.95</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>10.44</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>3.39</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>0.34</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-6.13</v>
+        <v>-4.53</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-15.35</v>
+        <v>-14.66</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-18.06</v>
+        <v>-19.89</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-20.66</v>
+        <v>-21.04</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-23.48</v>
+        <v>-22.81</v>
       </c>
     </row>
   </sheetData>
@@ -625,8 +625,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>341.3</v>
+        <v>340.3</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>125.5</v>
+        <v>124.8</v>
       </c>
     </row>
     <row r="4">
@@ -709,18 +709,18 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>113.5</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,18 +729,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>110.1</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>97.2</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>94.2</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>92.90000000000001</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>84.7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>83.8</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>82.59999999999999</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,18 +869,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>81.5</v>
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>77.59999999999999</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,18 +909,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>76.3</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,18 +929,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>75.5</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,18 +949,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>74.40000000000001</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>72.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,38 +1009,38 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>72.2</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>70.40000000000001</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Stanmore Resources</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,38 +1049,38 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>68.2</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>67.8</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>66.8</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,47 +1109,47 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>65.59999999999999</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>63.8</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>63.5</v>
+        <v>58.6</v>
       </c>
     </row>
   </sheetData>
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>104</v>
+        <v>103.9</v>
       </c>
     </row>
     <row r="4">
@@ -1249,7 +1249,7 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>79.3</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1262,7 +1262,7 @@
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>78.59999999999999</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1301,7 +1301,7 @@
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>72.3</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="11">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="14">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>64.59999999999999</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="16">
@@ -1398,27 +1398,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>63.3</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>63.1</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="19">
@@ -1431,7 +1431,7 @@
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.7</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="20">
@@ -1444,7 +1444,7 @@
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.4</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>59.8</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="22">
@@ -1483,7 +1483,7 @@
         <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="24">
@@ -1509,7 +1509,7 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.5</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="26">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-57.3</v>
+        <v>-57.1</v>
       </c>
     </row>
     <row r="19">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-50.4</v>
+        <v>-50.3</v>
       </c>
     </row>
     <row r="24">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.41</v>
+        <v>49.49</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.53</v>
+        <v>45.55</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43.98</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.57</v>
+        <v>40.67</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.57</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.53</v>
+        <v>32.67</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.53</v>
+        <v>27.55</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.36</v>
+        <v>27.43</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.83</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.86</v>
+        <v>13.88</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>42.57</v>
+        <v>46.34</v>
       </c>
     </row>
     <row r="3">
@@ -478,46 +478,46 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>17.38</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>11.37</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>8.43</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>4.31</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.03</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.53</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-14.66</v>
+        <v>-13.64</v>
       </c>
     </row>
     <row r="10">
@@ -569,33 +569,33 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-19.89</v>
+        <v>-18.35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-21.04</v>
+        <v>-22.04</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-22.81</v>
+        <v>-26.02</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>340.3</v>
+        <v>197.8</v>
       </c>
     </row>
     <row r="3">
@@ -689,27 +689,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>124.8</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>97</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="5">
@@ -729,27 +729,27 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>95.3</v>
+        <v>103.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>93.7</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -769,38 +769,38 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>84.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>83.3</v>
+        <v>85.59999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>83</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>81</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,38 +869,38 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>79.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>73.8</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>73.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -929,18 +929,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>70.09999999999999</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,18 +949,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>68.90000000000001</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>67.40000000000001</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>67.09999999999999</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Stanmore Resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>65.5</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>63.7</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Stanmore Resources</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,38 +1049,38 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>61.6</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>60.1</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>59.9</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,38 +1109,38 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>59.7</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>58.6</v>
+        <v>60.6</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>132.6</v>
+        <v>123.3</v>
       </c>
     </row>
     <row r="3">
@@ -1236,176 +1236,176 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>100.1</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>CTD</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>79.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>79.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>78.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TUA</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>76.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>TUA</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>72.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>72.5</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>71.3</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>69.90000000000001</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>67.2</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>66.7</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>64.8</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>64.09999999999999</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>63.4</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="18">
@@ -1418,65 +1418,65 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>63.4</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.8</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>59.9</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>58.3</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1489,14 +1489,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>57.8</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="25">
@@ -1515,14 +1515,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.2</v>
+        <v>57.6</v>
       </c>
     </row>
   </sheetData>
@@ -1576,376 +1576,376 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TUA</t>
+          <t>CTD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tuas</t>
+          <t>Corporate Travel Management</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-76</v>
+        <v>-85.59999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DRO</t>
+          <t>TUA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Droneshield</t>
+          <t>Tuas</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-74.3</v>
+        <v>-76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>DRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wisetech Global</t>
+          <t>Droneshield</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-71</v>
+        <v>-74.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zip</t>
+          <t>Wisetech Global</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-70</v>
+        <v>-70.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COH</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cochlear</t>
+          <t>Zip</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-69.7</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>COH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Life360</t>
+          <t>Cochlear</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-67.7</v>
+        <v>-69.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PME</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pro Medicus</t>
+          <t>Life360</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-66.2</v>
+        <v>-67.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>PME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>Pro Medicus</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-63.4</v>
+        <v>-66.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XRO</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Xero</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-62.4</v>
+        <v>-63.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>XRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Austal</t>
+          <t>Xero</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-61.3</v>
+        <v>-62.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>Austal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-60.3</v>
+        <v>-61.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-59.6</v>
+        <v>-60.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Seek</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-58.7</v>
+        <v>-59.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deep Yellow</t>
+          <t>Seek</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-58.2</v>
+        <v>-58.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>Deep Yellow</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-57.7</v>
+        <v>-58.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-57.5</v>
+        <v>-57.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TWE</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Treasury Wine Estates</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-57.1</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LLC</t>
+          <t>TWE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lendlease</t>
+          <t>Treasury Wine Estates</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-56.6</v>
+        <v>-57.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>LLC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ARB Corporation</t>
+          <t>Lendlease</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-56.4</v>
+        <v>-56.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>ARB Corporation</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-54.3</v>
+        <v>-56.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Catalyst Metals</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-51</v>
+        <v>-54.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LOV</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lovisa</t>
+          <t>Regis Healthcare</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-50.3</v>
+        <v>-52.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Champion Iron</t>
+          <t>Catalyst Metals</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-49.7</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PMV</t>
+          <t>LOV</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Premier Investments</t>
+          <t>Lovisa</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-49.1</v>
+        <v>-50.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Telix Pharmaceuticals</t>
+          <t>Champion Iron</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-49.1</v>
+        <v>-49.7</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.49</v>
+        <v>49.56</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.55</v>
+        <v>45.51</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.07</v>
+        <v>44.13</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.67</v>
+        <v>40.73</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.6</v>
+        <v>36.63</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.67</v>
+        <v>32.63</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.55</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.43</v>
+        <v>27.44</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.84</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.03</v>
+        <v>22.05</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.88</v>
+        <v>13.89</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>46.34</v>
+        <v>48.05</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>20.52</v>
+        <v>18.76</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>9.09</v>
+        <v>8.470000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>5.24</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>2.46</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>1.47</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.28</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-13.64</v>
+        <v>-13.99</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-18.35</v>
+        <v>-18.75</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-22.04</v>
+        <v>-21.57</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-26.02</v>
+        <v>-25.93</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>197.8</v>
+        <v>174.8</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>130.2</v>
+        <v>122.4</v>
       </c>
     </row>
     <row r="4">
@@ -709,18 +709,18 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>106.4</v>
+        <v>113.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,38 +729,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>103.6</v>
+        <v>107.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>97.40000000000001</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -769,18 +769,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>85.90000000000001</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,38 +789,38 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>85.59999999999999</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>84.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>83.8</v>
+        <v>85.59999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>80.8</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="12">
@@ -869,27 +869,27 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>80.40000000000001</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>80.3</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="14">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>78.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -929,38 +929,38 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>76.09999999999999</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>75.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Stanmore Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>74.40000000000001</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>74.3</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Stanmore Resources</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>70.09999999999999</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>68.5</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>65.7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,38 +1069,38 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>64.59999999999999</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>63.4</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Genesis Minerals</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,47 +1109,47 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>62.3</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>60.8</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>60.6</v>
+        <v>60.9</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>123.3</v>
+        <v>122.7</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>103.9</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>99.7</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="5">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79.40000000000001</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>78.90000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
@@ -1301,7 +1301,7 @@
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>76.09999999999999</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="10">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>73.09999999999999</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="11">
@@ -1327,7 +1327,7 @@
         <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>72.59999999999999</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="12">
@@ -1340,7 +1340,7 @@
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>71.3</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>69.90000000000001</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
         <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>64.7</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="17">
@@ -1411,27 +1411,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>63.5</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>63.4</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="20">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>61.5</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="22">
@@ -1470,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>59.8</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="23">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-85.59999999999999</v>
+        <v>-86</v>
       </c>
     </row>
     <row r="3">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-57.1</v>
+        <v>-57</v>
       </c>
     </row>
     <row r="20">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.56</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.51</v>
+        <v>45.35</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.13</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.73</v>
+        <v>40.74</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.63</v>
+        <v>36.62</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.63</v>
+        <v>32.56</v>
       </c>
     </row>
     <row r="8">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.86</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.05</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.89</v>
+        <v>13.87</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>48.05</v>
+        <v>44.01</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>18.76</v>
+        <v>21.57</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>8.470000000000001</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="5">
@@ -504,46 +504,46 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>3.82</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>1.43</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>0.92</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.7</v>
+        <v>-8.050000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-13.99</v>
+        <v>-14.88</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-18.75</v>
+        <v>-22.14</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-21.57</v>
+        <v>-23.38</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.93</v>
+        <v>-26.65</v>
       </c>
     </row>
   </sheetData>
@@ -655,32 +655,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>174.8</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -689,18 +689,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>122.4</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,18 +709,18 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>113.8</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,18 +729,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>107.6</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -749,18 +749,18 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>100.5</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -769,58 +769,58 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>94.3</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>92.3</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>91.40000000000001</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Stanmore Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>85.59999999999999</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,38 +849,38 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>83.8</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>81.5</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>81.5</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>80.90000000000001</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="15">
@@ -929,38 +929,38 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>79.59999999999999</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stanmore Resources</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>77.8</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>74</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>69.8</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1029,27 +1029,27 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>69.7</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>69</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1069,58 +1069,58 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>68.5</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>62.6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Genesis Minerals</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>62.2</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>61.4</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>60.9</v>
+        <v>56.1</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C2" t="n">
-        <v>122.7</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C3" t="n">
-        <v>104</v>
+        <v>104.1</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C4" t="n">
-        <v>99.5</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C5" t="n">
-        <v>85.09999999999999</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="6">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
         <v>79.59999999999999</v>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C7" t="n">
         <v>79.5</v>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C8" t="n">
-        <v>79</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C9" t="n">
-        <v>76.2</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C10" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1324,36 +1324,36 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C11" t="n">
-        <v>72.7</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C12" t="n">
-        <v>70.09999999999999</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C14" t="n">
-        <v>67.09999999999999</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C15" t="n">
-        <v>66.7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C16" t="n">
-        <v>64.8</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C17" t="n">
-        <v>64.2</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C18" t="n">
-        <v>63.4</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="19">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C19" t="n">
-        <v>63.3</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C20" t="n">
-        <v>61.9</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C21" t="n">
-        <v>61.4</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="22">
@@ -1467,33 +1467,33 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C22" t="n">
-        <v>59.7</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C23" t="n">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C24" t="n">
         <v>58.3</v>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C25" t="n">
-        <v>57.8</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="26">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C26" t="n">
-        <v>57.6</v>
+        <v>57.5</v>
       </c>
     </row>
   </sheetData>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-86</v>
+        <v>-86.3</v>
       </c>
     </row>
     <row r="3">
@@ -1831,46 +1831,46 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TWE</t>
+          <t>LLC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Treasury Wine Estates</t>
+          <t>Lendlease</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-57</v>
+        <v>-56.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LLC</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lendlease</t>
+          <t>ARB Corporation</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-56.6</v>
+        <v>-56.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>TWE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ARB Corporation</t>
+          <t>Treasury Wine Estates</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-56.4</v>
+        <v>-55.9</v>
       </c>
     </row>
     <row r="22">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.35</v>
+        <v>45.18</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.1</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.74</v>
+        <v>40.79</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.62</v>
+        <v>36.51</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.56</v>
+        <v>32.46</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.6</v>
+        <v>27.57</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.44</v>
+        <v>27.41</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.84</v>
+        <v>22.98</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.03</v>
+        <v>22.02</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.87</v>
+        <v>13.85</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>44.01</v>
+        <v>41.66</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>21.57</v>
+        <v>21.83</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>7.49</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>2.81</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>0.52</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>-3.08</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-8.050000000000001</v>
+        <v>-8.199999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-14.88</v>
+        <v>-16.11</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-22.14</v>
+        <v>-23.4</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-23.38</v>
+        <v>-24.15</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-26.65</v>
+        <v>-27.43</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +625,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
@@ -655,12 +655,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -669,18 +669,18 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>100.6</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -689,18 +689,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>99.3</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,38 +709,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>98.7</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>93.90000000000001</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -749,18 +749,18 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>85.8</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -769,38 +769,38 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>82.7</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>81.8</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Stanmore Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -809,18 +809,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>81.2</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stanmore Resources</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>80.09999999999999</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>79.8</v>
+        <v>74.09999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -869,18 +869,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>75.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>73.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,18 +909,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>73.8</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,18 +929,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>72.40000000000001</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,38 +949,38 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>68.8</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>68.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>67.8</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>66.90000000000001</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,98 +1029,98 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>66.8</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>64.59999999999999</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>62.7</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>59.6</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>58.4</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>56.1</v>
+        <v>54.4</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>111.5</v>
+        <v>111.4</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>104.1</v>
+        <v>103.9</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>99.7</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>85.3</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>79.59999999999999</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79.5</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>75.90000000000001</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="11">
@@ -1324,205 +1324,205 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>70.2</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>69.8</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>67.2</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>64.90000000000001</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>64.09999999999999</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>63.5</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>63.4</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>62</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>61.5</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>ILU</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>59.8</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>58.4</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>58.3</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.9</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.5</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.58</v>
+        <v>50.33</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.18</v>
+        <v>45.12</v>
       </c>
     </row>
     <row r="4">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.79</v>
+        <v>40.78</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.51</v>
+        <v>36.49</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.46</v>
+        <v>32.43</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.57</v>
+        <v>27.56</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.41</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.98</v>
+        <v>23.01</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.02</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.85</v>
+        <v>13.83</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>41.66</v>
+        <v>41.22</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>21.83</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>7.41</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>3.36</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.36</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>-4.25</v>
+        <v>-4.91</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-5.02</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-16.11</v>
+        <v>-16.68</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-23.4</v>
+        <v>-23.51</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-24.15</v>
+        <v>-24.86</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-27.43</v>
+        <v>-28.39</v>
       </c>
     </row>
   </sheetData>
@@ -655,12 +655,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -669,18 +669,18 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>102.4</v>
+        <v>110.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -689,78 +689,78 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>100.6</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>95.90000000000001</v>
+        <v>106.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>85.3</v>
+        <v>84.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>82.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -769,18 +769,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>81.7</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>81.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>80.7</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="10">
@@ -829,58 +829,58 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>79.2</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>74.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>73.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>73.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,18 +909,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>72.59999999999999</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,18 +929,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>69.5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Westgold Resources</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,38 +949,38 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>67.8</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>65.90000000000001</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>65.90000000000001</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>65.7</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>65.59999999999999</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,58 +1049,58 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>61</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>60.5</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>60.2</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,47 +1109,47 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>57.4</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>54.9</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>54.4</v>
+        <v>58.7</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>111.4</v>
+        <v>107.9</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>103.9</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="4">
@@ -1249,7 +1249,7 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>85.09999999999999</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="6">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>78.40000000000001</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
@@ -1327,7 +1327,7 @@
         <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="12">
@@ -1340,7 +1340,7 @@
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>69.7</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="13">
@@ -1366,7 +1366,7 @@
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>66.90000000000001</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>64.8</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1398,27 +1398,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>63.4</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>63.3</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="19">
@@ -1431,7 +1431,7 @@
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.8</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="20">
@@ -1483,7 +1483,7 @@
         <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="24">
@@ -1509,7 +1509,7 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.5</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="26">
@@ -1522,7 +1522,7 @@
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57</v>
+        <v>56.9</v>
       </c>
     </row>
   </sheetData>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-86.3</v>
+        <v>-87.59999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-76</v>
+        <v>-75.5</v>
       </c>
     </row>
     <row r="4">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.12</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.07</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.78</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.49</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.43</v>
+        <v>32.42</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.56</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.4</v>
+        <v>27.43</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.01</v>
+        <v>23.02</v>
       </c>
     </row>
     <row r="11">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.83</v>
+        <v>13.86</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>41.22</v>
+        <v>44.14</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>23.52</v>
+        <v>23.47</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>7.81</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>3.51</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="6">
@@ -517,33 +517,33 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.01</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-4.91</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.02</v>
+        <v>-5.85</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-16.68</v>
+        <v>-17.56</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-23.51</v>
+        <v>-25.11</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-24.86</v>
+        <v>-25.18</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-28.39</v>
+        <v>-28.26</v>
       </c>
     </row>
   </sheetData>
@@ -669,58 +669,58 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>110.7</v>
+        <v>148.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>108.7</v>
+        <v>118.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>106.6</v>
+        <v>111.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,27 +729,27 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>84.3</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>83.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -769,18 +769,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>83.2</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,27 +789,27 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>82.90000000000001</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Stanmore Resources</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>81.5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -829,27 +829,27 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>76.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Stanmore Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>76.59999999999999</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="12">
@@ -869,18 +869,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>76.09999999999999</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>70.40000000000001</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="14">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>69</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="15">
@@ -929,38 +929,38 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>67</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Westgold Resources</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>66.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,38 +969,38 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>66.09999999999999</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>64.09999999999999</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Regis Resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>64</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>62.9</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,107 +1049,107 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>62.3</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>61.1</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>60.9</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>59.6</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>58.9</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>58.7</v>
+        <v>58.2</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>107.9</v>
+        <v>107.7</v>
       </c>
     </row>
     <row r="3">
@@ -1249,7 +1249,7 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>85.7</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1268,27 +1268,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79.3</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>78</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="9">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>67.09999999999999</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14">
@@ -1366,7 +1366,7 @@
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>67.09999999999999</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1405,7 +1405,7 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>63.7</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="18">
@@ -1418,7 +1418,7 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>63.4</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="19">
@@ -1444,7 +1444,7 @@
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.4</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="21">
@@ -1457,72 +1457,72 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>59.7</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ILU</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>58.3</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>58.1</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>57.8</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.6</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>RRL</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>56.9</v>
+        <v>56.7</v>
       </c>
     </row>
   </sheetData>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-75.5</v>
+        <v>-75.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50.33</v>
+        <v>50.32</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.04</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.1</v>
+        <v>44.11</v>
       </c>
     </row>
     <row r="5">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.5</v>
+        <v>36.46</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.42</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.59</v>
+        <v>27.61</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.43</v>
+        <v>27.41</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.02</v>
+        <v>23.04</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.86</v>
+        <v>13.84</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>44.14</v>
+        <v>37.38</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>23.47</v>
+        <v>20.85</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>7.37</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>1.21</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="6">
@@ -517,33 +517,33 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.1</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>-5.32</v>
+        <v>-5.57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.85</v>
+        <v>-7.91</v>
       </c>
     </row>
     <row r="9">
@@ -556,33 +556,33 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-17.56</v>
+        <v>-19.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>-25.11</v>
+        <v>-25.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-25.18</v>
+        <v>-25.61</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-28.26</v>
+        <v>-28.49</v>
       </c>
     </row>
   </sheetData>
@@ -669,38 +669,38 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>148.1</v>
+        <v>131.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>118.9</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,18 +709,18 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>111.2</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,18 +729,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>93.7</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -749,78 +749,78 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>87.90000000000001</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>86.3</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>85.8</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>83</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Stanmore Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>81.90000000000001</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stanmore Resources</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>80.3</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,38 +869,38 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>79.7</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>77.7</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Mineral Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,118 +909,118 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>76.5</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>73.8</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>72.09999999999999</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>63.3</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>63</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Regis Resources</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>61.8</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,27 +1029,27 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>61.3</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>60.7</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="22">
@@ -1069,58 +1069,58 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>60.7</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>60.2</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>58.6</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>58.5</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>58.2</v>
+        <v>50.6</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>107.7</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>103.8</v>
+        <v>103.7</v>
       </c>
     </row>
     <row r="4">
@@ -1249,7 +1249,7 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>85.90000000000001</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1262,7 +1262,7 @@
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>79.5</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>77.2</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="9">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>72.8</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="14">
@@ -1366,7 +1366,7 @@
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>64.90000000000001</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1418,13 +1418,13 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>63.3</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1437,14 +1437,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.3</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="22">
@@ -1496,33 +1496,33 @@
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>CSC</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>56.9</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RRL</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>56.7</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1591,31 +1591,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TUA</t>
+          <t>DRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tuas</t>
+          <t>Droneshield</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-75.09999999999999</v>
+        <v>-74.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DRO</t>
+          <t>TUA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Droneshield</t>
+          <t>Tuas</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-74.8</v>
+        <v>-74.5</v>
       </c>
     </row>
     <row r="5">
@@ -1921,12 +1921,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LOV</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lovisa</t>
+          <t>Champion Iron</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1936,16 +1936,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>LOV</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Champion Iron</t>
+          <t>Lovisa</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-49.7</v>
+        <v>-49.5</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50.32</v>
+        <v>50.36</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.9</v>
+        <v>44.88</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.11</v>
+        <v>44.13</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.83</v>
+        <v>40.88</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.46</v>
+        <v>36.47</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.4</v>
+        <v>32.38</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.61</v>
+        <v>27.63</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.41</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.04</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.99</v>
+        <v>21.89</v>
       </c>
     </row>
     <row r="12">
